--- a/Assets/Plantillas/PlantillaBUFINS.xlsx
+++ b/Assets/Plantillas/PlantillaBUFINS.xlsx
@@ -1,547 +1,151 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\omara_\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8FE3CA-3816-4521-9BD1-C12C0B459522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="4" activeTab="8" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Z_BalancePrueba" sheetId="1" r:id="rId1"/>
-    <sheet name="Z_CteYnoCte" sheetId="2" r:id="rId2"/>
-    <sheet name="Z_PYGDetallado" sheetId="3" r:id="rId3"/>
-    <sheet name="Z_PYGDetalladoConAjuste" sheetId="4" r:id="rId4"/>
-    <sheet name="Z_PresupuestoBalance" sheetId="5" r:id="rId5"/>
-    <sheet name="Z_PptoPYGDetallado" sheetId="6" r:id="rId6"/>
-    <sheet name="Z_PptoPYGDetalladoConAjuste" sheetId="7" r:id="rId7"/>
-    <sheet name="Z_PCH" sheetId="8" r:id="rId8"/>
-    <sheet name="Z_EjecPCH" sheetId="9" r:id="rId9"/>
-    <sheet name="Datos" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_BalancePrueba" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_CteYnoCte" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_PYGDetallado" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_PYGDetalladoConAjuste" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_PresupuestoBalance" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_PptoPYGDetallado" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_PptoPYGDetalladoConAjuste" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_PCH" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_EjecPCH" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="10" state="hidden" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="Lista_AcPa">Datos!$C$2:$C$5</definedName>
     <definedName name="Lista_Ajuste1">Datos!$A$2:$A$3</definedName>
     <definedName name="Lista_Ajuste2">Datos!$B$2:$B$4</definedName>
+    <definedName name="Lista_Pais">Datos!$D$2:$D$36</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
-    El  Z_BalancePrueba debe estar a 1, 2, 4 y 6 dígitos del PUC</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
-    Las cuentas Z_CteYnoCte deben estar a 4 dígitos del PUC. Solo debe incluir las cuentas de balance que tienen porción corriente y no corriente e incluir el movimiento completo de las cuentas. </t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
-    Las cuentas Z_PYGDetallado deben estar a 6 dígitos del PUC</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
-    Las cuentas Z_PYGDetalladoConAjuste deben estar a 6 dígitos del PUC</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
-    Las cuentas Z_PresupuestoBalance deben estar a 1, 2, 4 y 6 dígitos del PUC</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
-    Las cuentas Z_PptoPYGDetallado deben estar a 6 dígitos del PUC</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
-    Las cuentas Z_PptoPYGDetalladoConAjuste deben estar a 6 dígitos del PUC</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
-    Las cuentas Z_PCH son las que se detallan en esta plantilla</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
-    Las cuentas Z_PCH son las que se detallan en esta plantilla</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="48">
-  <si>
-    <t>Cuenta</t>
-  </si>
-  <si>
-    <t>Descripcion</t>
-  </si>
-  <si>
-    <t>SaldoAnterior</t>
-  </si>
-  <si>
-    <t>Debito</t>
-  </si>
-  <si>
-    <t>Credito</t>
-  </si>
-  <si>
-    <t>NuevoSaldo</t>
-  </si>
-  <si>
-    <t>Empresa</t>
-  </si>
-  <si>
-    <t>Pais</t>
-  </si>
-  <si>
-    <t>Año</t>
-  </si>
-  <si>
-    <t>Mes</t>
-  </si>
-  <si>
-    <t>AcPa</t>
-  </si>
-  <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t>LineaNegocio</t>
-  </si>
-  <si>
-    <t>Ajuste1</t>
-  </si>
-  <si>
-    <t>Ajuste2</t>
-  </si>
-  <si>
-    <t>Nombre</t>
-  </si>
-  <si>
-    <t>Presupuesto</t>
-  </si>
-  <si>
-    <t>Saldo</t>
-  </si>
-  <si>
-    <t>Valor</t>
-  </si>
-  <si>
-    <t>Ingresos</t>
-  </si>
-  <si>
-    <t>Gastos de personal</t>
-  </si>
-  <si>
-    <t>Honorarios</t>
-  </si>
-  <si>
-    <t>Impuestos</t>
-  </si>
-  <si>
-    <t>Arrendamientos</t>
-  </si>
-  <si>
-    <t>Contribuciones y afiliaciones</t>
-  </si>
-  <si>
-    <t>Seguros</t>
-  </si>
-  <si>
-    <t>Servicios</t>
-  </si>
-  <si>
-    <t>Gastos legales</t>
-  </si>
-  <si>
-    <t>Mantenimiento y reparaciones</t>
-  </si>
-  <si>
-    <t>Adecuación e instalación</t>
-  </si>
-  <si>
-    <t>Gastos de viaje</t>
-  </si>
-  <si>
-    <t>Diversos</t>
-  </si>
-  <si>
-    <t>Provisión Cartera</t>
-  </si>
-  <si>
-    <t>Provisión Inventario</t>
-  </si>
-  <si>
-    <t>Otras ventas</t>
-  </si>
-  <si>
-    <t>Recuperaciones</t>
-  </si>
-  <si>
-    <t>Pérdida en venta y retiro de bienes</t>
-  </si>
-  <si>
-    <t>Gastos extraordinarios</t>
-  </si>
-  <si>
-    <t>Gastos diversos</t>
-  </si>
-  <si>
-    <t>Ebitda</t>
-  </si>
-  <si>
-    <t>GASTOS FIJOS</t>
-  </si>
-  <si>
-    <t>ACTIVO CORRIENTE</t>
-  </si>
-  <si>
-    <t>No Ebitda</t>
-  </si>
-  <si>
-    <t>VARIABLES</t>
-  </si>
-  <si>
-    <t>ACTIVO NO CORRIENTE</t>
-  </si>
-  <si>
-    <t>OTROS GASTOS</t>
-  </si>
-  <si>
-    <t>PASIVO NO CORRIENTE</t>
-  </si>
-  <si>
-    <t>PASIVO CORRIENTE</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * \-??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * \-??_ ;_ @_ "/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* \-??\ _€_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
   </numFmts>
   <fonts count="17">
     <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <sz val="10"/>
     </font>
     <font>
-      <u/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="10"/>
       <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
+      <u val="single"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
+      <name val="Geomanist Light"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Geomanist Light"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Cyntho"/>
       <charset val="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF01E1D7"/>
       <name val="Cyntho"/>
       <charset val="1"/>
+      <b val="1"/>
+      <color rgb="FF01E1D7"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
       <name val="Cyntho"/>
       <charset val="1"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Cyntho"/>
       <charset val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Cyntho"/>
       <charset val="1"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="1"/>
       <name val="Cyntho"/>
       <charset val="1"/>
+      <color theme="1"/>
+      <sz val="8"/>
     </font>
     <font>
-      <sz val="8"/>
       <name val="Cyntho"/>
       <charset val="1"/>
+      <sz val="8"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="8"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
       <name val="Cyntho"/>
       <charset val="1"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -603,151 +207,151 @@
     </border>
   </borders>
   <cellStyleXfs count="184">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="49" fontId="16" fillId="2" borderId="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="166" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0"/>
@@ -782,7 +386,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="3" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="3" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="16" fillId="0" borderId="0"/>
@@ -791,242 +395,241 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="30">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="9" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="9" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="9" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="9" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="184">
-    <cellStyle name="Comma 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Estilo 1" xfId="3" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Hipervínculo 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
-    <cellStyle name="Millares [0] 2" xfId="145" xr:uid="{00000000-0005-0000-0000-000095000000}"/>
-    <cellStyle name="Millares [0] 2 2" xfId="146" xr:uid="{00000000-0005-0000-0000-000096000000}"/>
-    <cellStyle name="Millares [0] 2 2 2" xfId="147" xr:uid="{00000000-0005-0000-0000-000097000000}"/>
-    <cellStyle name="Millares [0] 2 2 2 2" xfId="148" xr:uid="{00000000-0005-0000-0000-000098000000}"/>
-    <cellStyle name="Millares [0] 2 2 3" xfId="149" xr:uid="{00000000-0005-0000-0000-000099000000}"/>
-    <cellStyle name="Millares [0] 2 2 4" xfId="150" xr:uid="{00000000-0005-0000-0000-00009A000000}"/>
-    <cellStyle name="Millares [0] 2 3" xfId="151" xr:uid="{00000000-0005-0000-0000-00009B000000}"/>
-    <cellStyle name="Millares [0] 2 3 2" xfId="152" xr:uid="{00000000-0005-0000-0000-00009C000000}"/>
-    <cellStyle name="Millares [0] 2 4" xfId="153" xr:uid="{00000000-0005-0000-0000-00009D000000}"/>
-    <cellStyle name="Millares [0] 2 5" xfId="154" xr:uid="{00000000-0005-0000-0000-00009E000000}"/>
-    <cellStyle name="Millares [0] 2 6" xfId="155" xr:uid="{00000000-0005-0000-0000-00009F000000}"/>
-    <cellStyle name="Millares [0] 3" xfId="156" xr:uid="{00000000-0005-0000-0000-0000A0000000}"/>
-    <cellStyle name="Millares [0] 3 2" xfId="157" xr:uid="{00000000-0005-0000-0000-0000A1000000}"/>
-    <cellStyle name="Millares [0] 3 2 2" xfId="158" xr:uid="{00000000-0005-0000-0000-0000A2000000}"/>
-    <cellStyle name="Millares [0] 3 3" xfId="159" xr:uid="{00000000-0005-0000-0000-0000A3000000}"/>
-    <cellStyle name="Millares [0] 3 3 2" xfId="160" xr:uid="{00000000-0005-0000-0000-0000A4000000}"/>
-    <cellStyle name="Millares [0] 3 4" xfId="161" xr:uid="{00000000-0005-0000-0000-0000A5000000}"/>
-    <cellStyle name="Millares [0] 3 5" xfId="162" xr:uid="{00000000-0005-0000-0000-0000A6000000}"/>
-    <cellStyle name="Millares [0] 3 6" xfId="163" xr:uid="{00000000-0005-0000-0000-0000A7000000}"/>
-    <cellStyle name="Millares [0] 4" xfId="164" xr:uid="{00000000-0005-0000-0000-0000A8000000}"/>
-    <cellStyle name="Millares [0] 4 2" xfId="165" xr:uid="{00000000-0005-0000-0000-0000A9000000}"/>
-    <cellStyle name="Millares [0] 5" xfId="166" xr:uid="{00000000-0005-0000-0000-0000AA000000}"/>
-    <cellStyle name="Millares [0] 6" xfId="167" xr:uid="{00000000-0005-0000-0000-0000AB000000}"/>
-    <cellStyle name="Millares 10" xfId="5" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="Millares 10 2" xfId="6" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="Millares 11" xfId="7" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="Millares 11 2" xfId="8" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="Millares 12" xfId="9" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="Millares 12 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="Millares 13" xfId="11" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="Millares 13 2" xfId="12" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="Millares 14" xfId="13" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="Millares 14 2" xfId="14" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
-    <cellStyle name="Millares 15" xfId="15" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
-    <cellStyle name="Millares 15 2" xfId="16" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
-    <cellStyle name="Millares 16" xfId="17" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
-    <cellStyle name="Millares 16 2" xfId="18" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
-    <cellStyle name="Millares 17" xfId="19" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
-    <cellStyle name="Millares 17 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
-    <cellStyle name="Millares 18" xfId="21" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
-    <cellStyle name="Millares 18 2" xfId="22" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
-    <cellStyle name="Millares 19" xfId="23" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
-    <cellStyle name="Millares 19 2" xfId="24" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
-    <cellStyle name="Millares 2" xfId="25" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
-    <cellStyle name="Millares 2 2" xfId="26" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
-    <cellStyle name="Millares 2 2 2" xfId="27" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
-    <cellStyle name="Millares 2 2 2 2" xfId="28" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
-    <cellStyle name="Millares 2 2 3" xfId="29" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
-    <cellStyle name="Millares 2 2 4" xfId="30" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
-    <cellStyle name="Millares 2 3" xfId="31" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
-    <cellStyle name="Millares 2 3 2" xfId="32" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
-    <cellStyle name="Millares 2 4" xfId="33" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
-    <cellStyle name="Millares 2 5" xfId="34" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
-    <cellStyle name="Millares 20" xfId="35" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
-    <cellStyle name="Millares 20 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
-    <cellStyle name="Millares 21" xfId="37" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
-    <cellStyle name="Millares 21 2" xfId="38" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
-    <cellStyle name="Millares 22" xfId="39" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
-    <cellStyle name="Millares 22 2" xfId="40" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
-    <cellStyle name="Millares 23" xfId="41" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
-    <cellStyle name="Millares 23 2" xfId="42" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
-    <cellStyle name="Millares 24" xfId="43" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
-    <cellStyle name="Millares 24 2" xfId="44" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
-    <cellStyle name="Millares 25" xfId="45" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="Millares 25 2" xfId="46" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="Millares 26" xfId="47" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="Millares 26 2" xfId="48" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="Millares 27" xfId="49" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="Millares 27 2" xfId="50" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="Millares 28" xfId="51" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="Millares 28 2" xfId="52" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="Millares 29" xfId="53" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="Millares 29 2" xfId="54" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="Millares 3" xfId="55" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="Millares 3 2" xfId="56" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
-    <cellStyle name="Millares 3 2 2" xfId="57" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
-    <cellStyle name="Millares 3 2 2 2" xfId="58" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
-    <cellStyle name="Millares 3 2 3" xfId="59" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
-    <cellStyle name="Millares 3 2 4" xfId="60" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
-    <cellStyle name="Millares 3 3" xfId="61" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
-    <cellStyle name="Millares 3 4" xfId="62" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
-    <cellStyle name="Millares 3 5" xfId="63" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
-    <cellStyle name="Millares 30" xfId="64" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
-    <cellStyle name="Millares 30 2" xfId="65" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
-    <cellStyle name="Millares 31" xfId="66" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
-    <cellStyle name="Millares 31 2" xfId="67" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
-    <cellStyle name="Millares 32" xfId="68" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
-    <cellStyle name="Millares 32 2" xfId="69" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
-    <cellStyle name="Millares 33" xfId="70" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
-    <cellStyle name="Millares 33 2" xfId="71" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
-    <cellStyle name="Millares 34" xfId="72" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
-    <cellStyle name="Millares 34 2" xfId="73" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
-    <cellStyle name="Millares 35" xfId="74" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
-    <cellStyle name="Millares 35 2" xfId="75" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
-    <cellStyle name="Millares 36" xfId="76" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
-    <cellStyle name="Millares 36 2" xfId="77" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
-    <cellStyle name="Millares 37" xfId="78" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
-    <cellStyle name="Millares 37 2" xfId="79" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
-    <cellStyle name="Millares 38" xfId="80" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
-    <cellStyle name="Millares 38 2" xfId="81" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
-    <cellStyle name="Millares 39" xfId="82" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
-    <cellStyle name="Millares 39 2" xfId="83" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
-    <cellStyle name="Millares 4" xfId="84" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
-    <cellStyle name="Millares 40" xfId="85" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
-    <cellStyle name="Millares 40 2" xfId="86" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
-    <cellStyle name="Millares 41" xfId="87" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
-    <cellStyle name="Millares 41 2" xfId="88" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
-    <cellStyle name="Millares 42" xfId="89" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
-    <cellStyle name="Millares 42 2" xfId="90" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
-    <cellStyle name="Millares 43" xfId="91" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
-    <cellStyle name="Millares 43 2" xfId="92" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
-    <cellStyle name="Millares 44" xfId="93" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
-    <cellStyle name="Millares 44 2" xfId="94" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
-    <cellStyle name="Millares 45" xfId="95" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
-    <cellStyle name="Millares 45 2" xfId="96" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
-    <cellStyle name="Millares 46" xfId="97" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
-    <cellStyle name="Millares 46 2" xfId="98" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
-    <cellStyle name="Millares 47" xfId="99" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
-    <cellStyle name="Millares 47 2" xfId="100" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
-    <cellStyle name="Millares 48" xfId="101" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
-    <cellStyle name="Millares 48 2" xfId="102" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
-    <cellStyle name="Millares 49" xfId="103" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
-    <cellStyle name="Millares 49 2" xfId="104" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
-    <cellStyle name="Millares 5" xfId="105" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
-    <cellStyle name="Millares 50" xfId="106" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
-    <cellStyle name="Millares 50 2" xfId="107" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
-    <cellStyle name="Millares 51" xfId="108" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
-    <cellStyle name="Millares 51 2" xfId="109" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
-    <cellStyle name="Millares 52" xfId="110" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
-    <cellStyle name="Millares 52 2" xfId="111" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
-    <cellStyle name="Millares 53" xfId="112" xr:uid="{00000000-0005-0000-0000-000074000000}"/>
-    <cellStyle name="Millares 53 2" xfId="113" xr:uid="{00000000-0005-0000-0000-000075000000}"/>
-    <cellStyle name="Millares 54" xfId="114" xr:uid="{00000000-0005-0000-0000-000076000000}"/>
-    <cellStyle name="Millares 54 2" xfId="115" xr:uid="{00000000-0005-0000-0000-000077000000}"/>
-    <cellStyle name="Millares 55" xfId="116" xr:uid="{00000000-0005-0000-0000-000078000000}"/>
-    <cellStyle name="Millares 55 2" xfId="117" xr:uid="{00000000-0005-0000-0000-000079000000}"/>
-    <cellStyle name="Millares 56" xfId="118" xr:uid="{00000000-0005-0000-0000-00007A000000}"/>
-    <cellStyle name="Millares 56 2" xfId="119" xr:uid="{00000000-0005-0000-0000-00007B000000}"/>
-    <cellStyle name="Millares 57" xfId="120" xr:uid="{00000000-0005-0000-0000-00007C000000}"/>
-    <cellStyle name="Millares 58" xfId="121" xr:uid="{00000000-0005-0000-0000-00007D000000}"/>
-    <cellStyle name="Millares 59" xfId="122" xr:uid="{00000000-0005-0000-0000-00007E000000}"/>
-    <cellStyle name="Millares 6" xfId="123" xr:uid="{00000000-0005-0000-0000-00007F000000}"/>
-    <cellStyle name="Millares 60" xfId="124" xr:uid="{00000000-0005-0000-0000-000080000000}"/>
-    <cellStyle name="Millares 61" xfId="125" xr:uid="{00000000-0005-0000-0000-000081000000}"/>
-    <cellStyle name="Millares 62" xfId="126" xr:uid="{00000000-0005-0000-0000-000082000000}"/>
-    <cellStyle name="Millares 63" xfId="127" xr:uid="{00000000-0005-0000-0000-000083000000}"/>
-    <cellStyle name="Millares 64" xfId="128" xr:uid="{00000000-0005-0000-0000-000084000000}"/>
-    <cellStyle name="Millares 65" xfId="129" xr:uid="{00000000-0005-0000-0000-000085000000}"/>
-    <cellStyle name="Millares 7" xfId="130" xr:uid="{00000000-0005-0000-0000-000086000000}"/>
-    <cellStyle name="Millares 7 2" xfId="131" xr:uid="{00000000-0005-0000-0000-000087000000}"/>
-    <cellStyle name="Millares 7 2 2" xfId="132" xr:uid="{00000000-0005-0000-0000-000088000000}"/>
-    <cellStyle name="Millares 7 3" xfId="133" xr:uid="{00000000-0005-0000-0000-000089000000}"/>
-    <cellStyle name="Millares 7 4" xfId="134" xr:uid="{00000000-0005-0000-0000-00008A000000}"/>
-    <cellStyle name="Millares 8" xfId="135" xr:uid="{00000000-0005-0000-0000-00008B000000}"/>
-    <cellStyle name="Millares 8 2" xfId="136" xr:uid="{00000000-0005-0000-0000-00008C000000}"/>
-    <cellStyle name="Millares 8 2 2" xfId="137" xr:uid="{00000000-0005-0000-0000-00008D000000}"/>
-    <cellStyle name="Millares 8 3" xfId="138" xr:uid="{00000000-0005-0000-0000-00008E000000}"/>
-    <cellStyle name="Millares 8 4" xfId="139" xr:uid="{00000000-0005-0000-0000-00008F000000}"/>
-    <cellStyle name="Millares 9" xfId="140" xr:uid="{00000000-0005-0000-0000-000090000000}"/>
-    <cellStyle name="Millares 9 2" xfId="141" xr:uid="{00000000-0005-0000-0000-000091000000}"/>
-    <cellStyle name="Millares 9 2 2" xfId="142" xr:uid="{00000000-0005-0000-0000-000092000000}"/>
-    <cellStyle name="Millares 9 3" xfId="143" xr:uid="{00000000-0005-0000-0000-000093000000}"/>
-    <cellStyle name="Millares 9 4" xfId="144" xr:uid="{00000000-0005-0000-0000-000094000000}"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="168" xr:uid="{00000000-0005-0000-0000-0000AC000000}"/>
-    <cellStyle name="Normal 11" xfId="169" xr:uid="{00000000-0005-0000-0000-0000AD000000}"/>
-    <cellStyle name="Normal 2" xfId="170" xr:uid="{00000000-0005-0000-0000-0000AE000000}"/>
-    <cellStyle name="Normal 2 2" xfId="171" xr:uid="{00000000-0005-0000-0000-0000AF000000}"/>
-    <cellStyle name="Normal 2 3" xfId="172" xr:uid="{00000000-0005-0000-0000-0000B0000000}"/>
-    <cellStyle name="Normal 2 4" xfId="173" xr:uid="{00000000-0005-0000-0000-0000B1000000}"/>
-    <cellStyle name="Normal 2 5" xfId="174" xr:uid="{00000000-0005-0000-0000-0000B2000000}"/>
-    <cellStyle name="Normal 3" xfId="175" xr:uid="{00000000-0005-0000-0000-0000B3000000}"/>
-    <cellStyle name="Normal 4" xfId="176" xr:uid="{00000000-0005-0000-0000-0000B4000000}"/>
-    <cellStyle name="Normal 5" xfId="177" xr:uid="{00000000-0005-0000-0000-0000B5000000}"/>
-    <cellStyle name="Normal 6" xfId="178" xr:uid="{00000000-0005-0000-0000-0000B6000000}"/>
-    <cellStyle name="Normal 6 2" xfId="179" xr:uid="{00000000-0005-0000-0000-0000B7000000}"/>
-    <cellStyle name="Normal 7" xfId="180" xr:uid="{00000000-0005-0000-0000-0000B8000000}"/>
-    <cellStyle name="Normal 8" xfId="181" xr:uid="{00000000-0005-0000-0000-0000B9000000}"/>
-    <cellStyle name="Normal 9" xfId="182" xr:uid="{00000000-0005-0000-0000-0000BA000000}"/>
-    <cellStyle name="Porcentaje 2" xfId="183" xr:uid="{00000000-0005-0000-0000-0000BB000000}"/>
+    <cellStyle name="Comma 2" xfId="2"/>
+    <cellStyle name="Estilo 1" xfId="3"/>
+    <cellStyle name="Hipervínculo 2" xfId="4"/>
+    <cellStyle name="Millares 10" xfId="5"/>
+    <cellStyle name="Millares 10 2" xfId="6"/>
+    <cellStyle name="Millares 11" xfId="7"/>
+    <cellStyle name="Millares 11 2" xfId="8"/>
+    <cellStyle name="Millares 12" xfId="9"/>
+    <cellStyle name="Millares 12 2" xfId="10"/>
+    <cellStyle name="Millares 13" xfId="11"/>
+    <cellStyle name="Millares 13 2" xfId="12"/>
+    <cellStyle name="Millares 14" xfId="13"/>
+    <cellStyle name="Millares 14 2" xfId="14"/>
+    <cellStyle name="Millares 15" xfId="15"/>
+    <cellStyle name="Millares 15 2" xfId="16"/>
+    <cellStyle name="Millares 16" xfId="17"/>
+    <cellStyle name="Millares 16 2" xfId="18"/>
+    <cellStyle name="Millares 17" xfId="19"/>
+    <cellStyle name="Millares 17 2" xfId="20"/>
+    <cellStyle name="Millares 18" xfId="21"/>
+    <cellStyle name="Millares 18 2" xfId="22"/>
+    <cellStyle name="Millares 19" xfId="23"/>
+    <cellStyle name="Millares 19 2" xfId="24"/>
+    <cellStyle name="Millares 2" xfId="25"/>
+    <cellStyle name="Millares 2 2" xfId="26"/>
+    <cellStyle name="Millares 2 2 2" xfId="27"/>
+    <cellStyle name="Millares 2 2 2 2" xfId="28"/>
+    <cellStyle name="Millares 2 2 3" xfId="29"/>
+    <cellStyle name="Millares 2 2 4" xfId="30"/>
+    <cellStyle name="Millares 2 3" xfId="31"/>
+    <cellStyle name="Millares 2 3 2" xfId="32"/>
+    <cellStyle name="Millares 2 4" xfId="33"/>
+    <cellStyle name="Millares 2 5" xfId="34"/>
+    <cellStyle name="Millares 20" xfId="35"/>
+    <cellStyle name="Millares 20 2" xfId="36"/>
+    <cellStyle name="Millares 21" xfId="37"/>
+    <cellStyle name="Millares 21 2" xfId="38"/>
+    <cellStyle name="Millares 22" xfId="39"/>
+    <cellStyle name="Millares 22 2" xfId="40"/>
+    <cellStyle name="Millares 23" xfId="41"/>
+    <cellStyle name="Millares 23 2" xfId="42"/>
+    <cellStyle name="Millares 24" xfId="43"/>
+    <cellStyle name="Millares 24 2" xfId="44"/>
+    <cellStyle name="Millares 25" xfId="45"/>
+    <cellStyle name="Millares 25 2" xfId="46"/>
+    <cellStyle name="Millares 26" xfId="47"/>
+    <cellStyle name="Millares 26 2" xfId="48"/>
+    <cellStyle name="Millares 27" xfId="49"/>
+    <cellStyle name="Millares 27 2" xfId="50"/>
+    <cellStyle name="Millares 28" xfId="51"/>
+    <cellStyle name="Millares 28 2" xfId="52"/>
+    <cellStyle name="Millares 29" xfId="53"/>
+    <cellStyle name="Millares 29 2" xfId="54"/>
+    <cellStyle name="Millares 3" xfId="55"/>
+    <cellStyle name="Millares 3 2" xfId="56"/>
+    <cellStyle name="Millares 3 2 2" xfId="57"/>
+    <cellStyle name="Millares 3 2 2 2" xfId="58"/>
+    <cellStyle name="Millares 3 2 3" xfId="59"/>
+    <cellStyle name="Millares 3 2 4" xfId="60"/>
+    <cellStyle name="Millares 3 3" xfId="61"/>
+    <cellStyle name="Millares 3 4" xfId="62"/>
+    <cellStyle name="Millares 3 5" xfId="63"/>
+    <cellStyle name="Millares 30" xfId="64"/>
+    <cellStyle name="Millares 30 2" xfId="65"/>
+    <cellStyle name="Millares 31" xfId="66"/>
+    <cellStyle name="Millares 31 2" xfId="67"/>
+    <cellStyle name="Millares 32" xfId="68"/>
+    <cellStyle name="Millares 32 2" xfId="69"/>
+    <cellStyle name="Millares 33" xfId="70"/>
+    <cellStyle name="Millares 33 2" xfId="71"/>
+    <cellStyle name="Millares 34" xfId="72"/>
+    <cellStyle name="Millares 34 2" xfId="73"/>
+    <cellStyle name="Millares 35" xfId="74"/>
+    <cellStyle name="Millares 35 2" xfId="75"/>
+    <cellStyle name="Millares 36" xfId="76"/>
+    <cellStyle name="Millares 36 2" xfId="77"/>
+    <cellStyle name="Millares 37" xfId="78"/>
+    <cellStyle name="Millares 37 2" xfId="79"/>
+    <cellStyle name="Millares 38" xfId="80"/>
+    <cellStyle name="Millares 38 2" xfId="81"/>
+    <cellStyle name="Millares 39" xfId="82"/>
+    <cellStyle name="Millares 39 2" xfId="83"/>
+    <cellStyle name="Millares 4" xfId="84"/>
+    <cellStyle name="Millares 40" xfId="85"/>
+    <cellStyle name="Millares 40 2" xfId="86"/>
+    <cellStyle name="Millares 41" xfId="87"/>
+    <cellStyle name="Millares 41 2" xfId="88"/>
+    <cellStyle name="Millares 42" xfId="89"/>
+    <cellStyle name="Millares 42 2" xfId="90"/>
+    <cellStyle name="Millares 43" xfId="91"/>
+    <cellStyle name="Millares 43 2" xfId="92"/>
+    <cellStyle name="Millares 44" xfId="93"/>
+    <cellStyle name="Millares 44 2" xfId="94"/>
+    <cellStyle name="Millares 45" xfId="95"/>
+    <cellStyle name="Millares 45 2" xfId="96"/>
+    <cellStyle name="Millares 46" xfId="97"/>
+    <cellStyle name="Millares 46 2" xfId="98"/>
+    <cellStyle name="Millares 47" xfId="99"/>
+    <cellStyle name="Millares 47 2" xfId="100"/>
+    <cellStyle name="Millares 48" xfId="101"/>
+    <cellStyle name="Millares 48 2" xfId="102"/>
+    <cellStyle name="Millares 49" xfId="103"/>
+    <cellStyle name="Millares 49 2" xfId="104"/>
+    <cellStyle name="Millares 5" xfId="105"/>
+    <cellStyle name="Millares 50" xfId="106"/>
+    <cellStyle name="Millares 50 2" xfId="107"/>
+    <cellStyle name="Millares 51" xfId="108"/>
+    <cellStyle name="Millares 51 2" xfId="109"/>
+    <cellStyle name="Millares 52" xfId="110"/>
+    <cellStyle name="Millares 52 2" xfId="111"/>
+    <cellStyle name="Millares 53" xfId="112"/>
+    <cellStyle name="Millares 53 2" xfId="113"/>
+    <cellStyle name="Millares 54" xfId="114"/>
+    <cellStyle name="Millares 54 2" xfId="115"/>
+    <cellStyle name="Millares 55" xfId="116"/>
+    <cellStyle name="Millares 55 2" xfId="117"/>
+    <cellStyle name="Millares 56" xfId="118"/>
+    <cellStyle name="Millares 56 2" xfId="119"/>
+    <cellStyle name="Millares 57" xfId="120"/>
+    <cellStyle name="Millares 58" xfId="121"/>
+    <cellStyle name="Millares 59" xfId="122"/>
+    <cellStyle name="Millares 6" xfId="123"/>
+    <cellStyle name="Millares 60" xfId="124"/>
+    <cellStyle name="Millares 61" xfId="125"/>
+    <cellStyle name="Millares 62" xfId="126"/>
+    <cellStyle name="Millares 63" xfId="127"/>
+    <cellStyle name="Millares 64" xfId="128"/>
+    <cellStyle name="Millares 65" xfId="129"/>
+    <cellStyle name="Millares 7" xfId="130"/>
+    <cellStyle name="Millares 7 2" xfId="131"/>
+    <cellStyle name="Millares 7 2 2" xfId="132"/>
+    <cellStyle name="Millares 7 3" xfId="133"/>
+    <cellStyle name="Millares 7 4" xfId="134"/>
+    <cellStyle name="Millares 8" xfId="135"/>
+    <cellStyle name="Millares 8 2" xfId="136"/>
+    <cellStyle name="Millares 8 2 2" xfId="137"/>
+    <cellStyle name="Millares 8 3" xfId="138"/>
+    <cellStyle name="Millares 8 4" xfId="139"/>
+    <cellStyle name="Millares 9" xfId="140"/>
+    <cellStyle name="Millares 9 2" xfId="141"/>
+    <cellStyle name="Millares 9 2 2" xfId="142"/>
+    <cellStyle name="Millares 9 3" xfId="143"/>
+    <cellStyle name="Millares 9 4" xfId="144"/>
+    <cellStyle name="Millares [0] 2" xfId="145"/>
+    <cellStyle name="Millares [0] 2 2" xfId="146"/>
+    <cellStyle name="Millares [0] 2 2 2" xfId="147"/>
+    <cellStyle name="Millares [0] 2 2 2 2" xfId="148"/>
+    <cellStyle name="Millares [0] 2 2 3" xfId="149"/>
+    <cellStyle name="Millares [0] 2 2 4" xfId="150"/>
+    <cellStyle name="Millares [0] 2 3" xfId="151"/>
+    <cellStyle name="Millares [0] 2 3 2" xfId="152"/>
+    <cellStyle name="Millares [0] 2 4" xfId="153"/>
+    <cellStyle name="Millares [0] 2 5" xfId="154"/>
+    <cellStyle name="Millares [0] 2 6" xfId="155"/>
+    <cellStyle name="Millares [0] 3" xfId="156"/>
+    <cellStyle name="Millares [0] 3 2" xfId="157"/>
+    <cellStyle name="Millares [0] 3 2 2" xfId="158"/>
+    <cellStyle name="Millares [0] 3 3" xfId="159"/>
+    <cellStyle name="Millares [0] 3 3 2" xfId="160"/>
+    <cellStyle name="Millares [0] 3 4" xfId="161"/>
+    <cellStyle name="Millares [0] 3 5" xfId="162"/>
+    <cellStyle name="Millares [0] 3 6" xfId="163"/>
+    <cellStyle name="Millares [0] 4" xfId="164"/>
+    <cellStyle name="Millares [0] 4 2" xfId="165"/>
+    <cellStyle name="Millares [0] 5" xfId="166"/>
+    <cellStyle name="Millares [0] 6" xfId="167"/>
+    <cellStyle name="Normal 10" xfId="168"/>
+    <cellStyle name="Normal 11" xfId="169"/>
+    <cellStyle name="Normal 2" xfId="170"/>
+    <cellStyle name="Normal 2 2" xfId="171"/>
+    <cellStyle name="Normal 2 3" xfId="172"/>
+    <cellStyle name="Normal 2 4" xfId="173"/>
+    <cellStyle name="Normal 2 5" xfId="174"/>
+    <cellStyle name="Normal 3" xfId="175"/>
+    <cellStyle name="Normal 4" xfId="176"/>
+    <cellStyle name="Normal 5" xfId="177"/>
+    <cellStyle name="Normal 6" xfId="178"/>
+    <cellStyle name="Normal 6 2" xfId="179"/>
+    <cellStyle name="Normal 7" xfId="180"/>
+    <cellStyle name="Normal 8" xfId="181"/>
+    <cellStyle name="Normal 9" xfId="182"/>
+    <cellStyle name="Porcentaje 2" xfId="183"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -1096,168 +699,322 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    El  Z_BalancePrueba debe estar a 1, 2, 4 y 6 dígitos del PUC</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Las cuentas Z_CteYnoCte deben estar a 4 dígitos del PUC. Solo debe incluir las cuentas de balance que tienen porción corriente y no corriente e incluir el movimiento completo de las cuentas. </t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Las cuentas Z_PYGDetallado deben estar a 6 dígitos del PUC</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Las cuentas Z_PYGDetalladoConAjuste deben estar a 6 dígitos del PUC</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Las cuentas Z_PresupuestoBalance deben estar a 1, 2, 4 y 6 dígitos del PUC</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Las cuentas Z_PptoPYGDetallado deben estar a 6 dígitos del PUC</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Las cuentas Z_PptoPYGDetalladoConAjuste deben estar a 6 dígitos del PUC</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Las cuentas Z_PCH son las que se detallan en esta plantilla</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Las cuentas Z_PCH son las que se detallan en esta plantilla</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaBalance" displayName="TablaBalance" ref="A1:J2" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaBalance" displayName="TablaBalance" ref="A1:J2" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Cuenta"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Descripcion"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="SaldoAnterior"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Debito"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Credito"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="NuevoSaldo"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Empresa"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Pais"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Año"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Mes" totalsRowFunction="sum"/>
+    <tableColumn id="1" name="Cuenta"/>
+    <tableColumn id="2" name="Descripcion"/>
+    <tableColumn id="3" name="SaldoAnterior"/>
+    <tableColumn id="4" name="Debito"/>
+    <tableColumn id="5" name="Credito"/>
+    <tableColumn id="6" name="NuevoSaldo"/>
+    <tableColumn id="7" name="Empresa"/>
+    <tableColumn id="8" name="Pais"/>
+    <tableColumn id="9" name="Año"/>
+    <tableColumn id="10" name="Mes" totalsRowFunction="sum"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TablaCteYNoCte" displayName="TablaCteYNoCte" ref="A1:K2" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TablaCteYNoCte" displayName="TablaCteYNoCte" ref="A1:K2" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Cuenta"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Descripcion"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="SaldoAnterior"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Debito"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Credito"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="NuevoSaldo"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Empresa"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Pais"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Año"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Mes"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="AcPa"/>
+    <tableColumn id="1" name="Cuenta"/>
+    <tableColumn id="2" name="Descripcion"/>
+    <tableColumn id="3" name="SaldoAnterior"/>
+    <tableColumn id="4" name="Debito"/>
+    <tableColumn id="5" name="Credito"/>
+    <tableColumn id="6" name="NuevoSaldo"/>
+    <tableColumn id="7" name="Empresa"/>
+    <tableColumn id="8" name="Pais"/>
+    <tableColumn id="9" name="Año"/>
+    <tableColumn id="10" name="Mes"/>
+    <tableColumn id="11" name="AcPa"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="TablaPYGDetallado" displayName="TablaPYGDetallado" ref="A1:K2" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TablaPYGDetallado" displayName="TablaPYGDetallado" ref="A1:K2" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Cuenta"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Descripcion"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Tipo"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="LineaNegocio"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="NuevoSaldo"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Empresa"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Pais"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Año"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Mes"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Ajuste1"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Ajuste2"/>
+    <tableColumn id="1" name="Cuenta"/>
+    <tableColumn id="2" name="Descripcion"/>
+    <tableColumn id="3" name="Tipo"/>
+    <tableColumn id="4" name="LineaNegocio"/>
+    <tableColumn id="5" name="NuevoSaldo"/>
+    <tableColumn id="6" name="Empresa"/>
+    <tableColumn id="7" name="Pais"/>
+    <tableColumn id="8" name="Año"/>
+    <tableColumn id="9" name="Mes"/>
+    <tableColumn id="10" name="Ajuste1"/>
+    <tableColumn id="11" name="Ajuste2"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="TablaPYGDetalladoConAjuste" displayName="TablaPYGDetalladoConAjuste" ref="A1:K2" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TablaPYGDetalladoConAjuste" displayName="TablaPYGDetalladoConAjuste" ref="A1:K2" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Cuenta"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Descripcion"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Tipo"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="LineaNegocio"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="NuevoSaldo"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Empresa"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Pais"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Año"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="Mes"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="Ajuste1"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="Ajuste2"/>
+    <tableColumn id="1" name="Cuenta"/>
+    <tableColumn id="2" name="Descripcion"/>
+    <tableColumn id="3" name="Tipo"/>
+    <tableColumn id="4" name="LineaNegocio"/>
+    <tableColumn id="5" name="NuevoSaldo"/>
+    <tableColumn id="6" name="Empresa"/>
+    <tableColumn id="7" name="Pais"/>
+    <tableColumn id="8" name="Año"/>
+    <tableColumn id="9" name="Mes"/>
+    <tableColumn id="10" name="Ajuste1"/>
+    <tableColumn id="11" name="Ajuste2"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="TablaPresupuesto" displayName="TablaPresupuesto" ref="A1:G2" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TablaPresupuesto" displayName="TablaPresupuesto" ref="A1:G2" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Cuenta"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Nombre"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Presupuesto"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Empresa"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Pais"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Año"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="Mes"/>
+    <tableColumn id="1" name="Cuenta"/>
+    <tableColumn id="2" name="Nombre"/>
+    <tableColumn id="3" name="Presupuesto"/>
+    <tableColumn id="4" name="Empresa"/>
+    <tableColumn id="5" name="Pais"/>
+    <tableColumn id="6" name="Año"/>
+    <tableColumn id="7" name="Mes"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="TablaPresupuestoDetallado" displayName="TablaPresupuestoDetallado" ref="A1:K2" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TablaPresupuestoDetallado" displayName="TablaPresupuestoDetallado" ref="A1:K2" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Cuenta"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Descripcion"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Tipo"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="LineaNegocio"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Saldo"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Empresa"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Pais"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="Año"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="Mes"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="Ajuste1"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="Ajuste2"/>
+    <tableColumn id="1" name="Cuenta"/>
+    <tableColumn id="2" name="Descripcion"/>
+    <tableColumn id="3" name="Tipo"/>
+    <tableColumn id="4" name="LineaNegocio"/>
+    <tableColumn id="5" name="Saldo"/>
+    <tableColumn id="6" name="Empresa"/>
+    <tableColumn id="7" name="Pais"/>
+    <tableColumn id="8" name="Año"/>
+    <tableColumn id="9" name="Mes"/>
+    <tableColumn id="10" name="Ajuste1"/>
+    <tableColumn id="11" name="Ajuste2"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="TablaPresupuestoDetallado18" displayName="TablaPresupuestoDetallado18" ref="A1:K2" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TablaPresupuestoDetallado18" displayName="TablaPresupuestoDetallado18" ref="A1:K2" headerRowCount="1" totalsRowShown="0">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Cuenta"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Descripcion"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Tipo"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="LineaNegocio"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="Saldo"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Empresa"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="Pais"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="Año"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="Mes"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="Ajuste1"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" name="Ajuste2"/>
+    <tableColumn id="1" name="Cuenta"/>
+    <tableColumn id="2" name="Descripcion"/>
+    <tableColumn id="3" name="Tipo"/>
+    <tableColumn id="4" name="LineaNegocio"/>
+    <tableColumn id="5" name="Saldo"/>
+    <tableColumn id="6" name="Empresa"/>
+    <tableColumn id="7" name="Pais"/>
+    <tableColumn id="8" name="Año"/>
+    <tableColumn id="9" name="Mes"/>
+    <tableColumn id="10" name="Ajuste1"/>
+    <tableColumn id="11" name="Ajuste2"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="TablaPCH" displayName="TablaPCH" ref="A1:E36" totalsRowShown="0">
-  <autoFilter ref="A1:E36" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="TablaPCH" displayName="TablaPCH" ref="A1:E36" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A1:E36"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Cuenta"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Nombre"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Valor"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Año"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="Mes"/>
+    <tableColumn id="1" name="Cuenta"/>
+    <tableColumn id="2" name="Nombre"/>
+    <tableColumn id="3" name="Valor"/>
+    <tableColumn id="4" name="Año"/>
+    <tableColumn id="5" name="Mes"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="TablaEjecPCH" displayName="TablaEjecPCH" ref="A1:E36" totalsRowShown="0">
-  <autoFilter ref="A1:E36" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="TablaEjecPCH" displayName="TablaEjecPCH" ref="A1:E36" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A1:E36"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="Cuenta"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="Nombre"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="Valor"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Año"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="Mes"/>
+    <tableColumn id="1" name="Cuenta"/>
+    <tableColumn id="2" name="Nombre"/>
+    <tableColumn id="3" name="Valor"/>
+    <tableColumn id="4" name="Año"/>
+    <tableColumn id="5" name="Mes"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1438,528 +1195,951 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF583AFF"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="25.28515625" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="13" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" customWidth="1"/>
-    <col min="4" max="5" width="13" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14" style="2" customWidth="1"/>
-    <col min="7" max="10" width="13" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="25.28515625" style="1"/>
+    <col width="13" customWidth="1" style="1" min="1" max="1"/>
+    <col width="15" customWidth="1" style="1" min="2" max="2"/>
+    <col width="17" customWidth="1" style="2" min="3" max="3"/>
+    <col width="13" customWidth="1" style="2" min="4" max="5"/>
+    <col width="14" customWidth="1" style="2" min="6" max="6"/>
+    <col width="13" customWidth="1" style="3" min="7" max="10"/>
+    <col width="25.28515625" customWidth="1" style="1" min="11" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="7" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>9</v>
+    <row r="1" ht="19.5" customFormat="1" customHeight="1" s="7">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Cuenta</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>SaldoAnterior</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Debito</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Credito</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>NuevoSaldo</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Pais</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="14.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="8" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="9" t="n"/>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="9" t="n"/>
+      <c r="F2" s="9" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="H2:H501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lista_Pais</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:C5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="3" width="18" customWidth="1"/>
+    <col width="18" customWidth="1" min="1" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="28" t="s">
-        <v>10</v>
+    <row r="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>Ajuste1</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>Ajuste2</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>AcPa</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Pais</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="29" t="s">
-        <v>41</v>
+    <row r="2">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>Ebitda</t>
+        </is>
+      </c>
+      <c r="B2" s="29" t="inlineStr">
+        <is>
+          <t>GASTOS FIJOS</t>
+        </is>
+      </c>
+      <c r="C2" s="29" t="inlineStr">
+        <is>
+          <t>ACTIVO CORRIENTE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Antigua y Barbuda</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>44</v>
+    <row r="3">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>No Ebitda</t>
+        </is>
+      </c>
+      <c r="B3" s="29" t="inlineStr">
+        <is>
+          <t>VARIABLES</t>
+        </is>
+      </c>
+      <c r="C3" s="29" t="inlineStr">
+        <is>
+          <t>ACTIVO NO CORRIENTE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="B4" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" s="29" t="s">
-        <v>46</v>
+    <row r="4">
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>OTROS GASTOS</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>PASIVO NO CORRIENTE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bahamas</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="C5" s="29" t="s">
-        <v>47</v>
+    <row r="5">
+      <c r="C5" s="29" t="inlineStr">
+        <is>
+          <t>PASIVO CORRIENTE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Barbados</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Belice</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Canadá</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Cuba</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Dominica</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Haití</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Nicaragua</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Panamá</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Perú</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>República Dominicana</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>San Cristóbal y Nieves</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>San Vicente y las Granadinas</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Santa Lucía</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Suriname</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Trinidad y Tobago</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF583AFF"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="26.5703125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="13" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="11" customWidth="1"/>
-    <col min="4" max="5" width="13" style="11" customWidth="1"/>
-    <col min="6" max="6" width="14" style="11" customWidth="1"/>
-    <col min="7" max="11" width="13" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="26.5703125" style="12"/>
+    <col width="13" customWidth="1" style="1" min="1" max="1"/>
+    <col width="15" customWidth="1" style="1" min="2" max="2"/>
+    <col width="17" customWidth="1" style="11" min="3" max="3"/>
+    <col width="13" customWidth="1" style="11" min="4" max="5"/>
+    <col width="14" customWidth="1" style="11" min="6" max="6"/>
+    <col width="13" customWidth="1" style="1" min="7" max="11"/>
+    <col width="26.5703125" customWidth="1" style="12" min="12" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>10</v>
+    <row r="1" ht="19.5" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Cuenta</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>SaldoAnterior</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>Debito</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Credito</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>NuevoSaldo</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Pais</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>AcPa</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="14.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="8"/>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="8" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="9" t="n"/>
+      <c r="D2" s="9" t="n"/>
+      <c r="E2" s="9" t="n"/>
+      <c r="F2" s="9" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="8" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K501" xr:uid="{00000000-0002-0000-0100-000000000000}">
+  <dataValidations count="2">
+    <dataValidation sqref="K2:K501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>Lista_AcPa</formula1>
       <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation sqref="H2:H501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lista_Pais</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF583AFF"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="13" style="12" customWidth="1"/>
-    <col min="2" max="2" width="15" style="12" customWidth="1"/>
-    <col min="3" max="3" width="13" style="12" customWidth="1"/>
-    <col min="4" max="4" width="16" style="12" customWidth="1"/>
-    <col min="5" max="5" width="14" style="13" customWidth="1"/>
-    <col min="6" max="7" width="13" style="12" customWidth="1"/>
-    <col min="8" max="8" width="13" style="14" customWidth="1"/>
-    <col min="9" max="11" width="13" style="12" customWidth="1"/>
-    <col min="12" max="16384" width="10.5703125" style="12"/>
+    <col width="13" customWidth="1" style="12" min="1" max="1"/>
+    <col width="15" customWidth="1" style="12" min="2" max="2"/>
+    <col width="13" customWidth="1" style="12" min="3" max="3"/>
+    <col width="16" customWidth="1" style="12" min="4" max="4"/>
+    <col width="14" customWidth="1" style="13" min="5" max="5"/>
+    <col width="13" customWidth="1" style="12" min="6" max="7"/>
+    <col width="13" customWidth="1" style="14" min="8" max="8"/>
+    <col width="13" customWidth="1" style="12" min="9" max="11"/>
+    <col width="10.5703125" customWidth="1" style="12" min="12" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>14</v>
+    <row r="1" ht="19.5" customFormat="1" customHeight="1" s="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Cuenta</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>LineaNegocio</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>NuevoSaldo</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Pais</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Ajuste1</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Ajuste2</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
+    <row r="2" ht="13.5" customFormat="1" customHeight="1" s="1">
+      <c r="A2" s="8" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="9" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="8" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J501" xr:uid="{00000000-0002-0000-0200-000000000000}">
+  <dataValidations count="3">
+    <dataValidation sqref="J2:J501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>Lista_Ajuste1</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K501" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation sqref="K2:K501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>Lista_Ajuste2</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation sqref="G2:G501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lista_Pais</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF583AFF"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="13" style="12" customWidth="1"/>
-    <col min="2" max="2" width="15" style="12" customWidth="1"/>
-    <col min="3" max="3" width="13" style="12" customWidth="1"/>
-    <col min="4" max="4" width="16" style="12" customWidth="1"/>
-    <col min="5" max="5" width="14" style="13" customWidth="1"/>
-    <col min="6" max="7" width="13" style="12" customWidth="1"/>
-    <col min="8" max="8" width="13" style="14" customWidth="1"/>
-    <col min="9" max="11" width="13" style="12" customWidth="1"/>
-    <col min="12" max="16384" width="10.5703125" style="12"/>
+    <col width="13" customWidth="1" style="12" min="1" max="1"/>
+    <col width="15" customWidth="1" style="12" min="2" max="2"/>
+    <col width="13" customWidth="1" style="12" min="3" max="3"/>
+    <col width="16" customWidth="1" style="12" min="4" max="4"/>
+    <col width="14" customWidth="1" style="13" min="5" max="5"/>
+    <col width="13" customWidth="1" style="12" min="6" max="7"/>
+    <col width="13" customWidth="1" style="14" min="8" max="8"/>
+    <col width="13" customWidth="1" style="12" min="9" max="11"/>
+    <col width="10.5703125" customWidth="1" style="12" min="12" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>14</v>
+    <row r="1" ht="19.5" customFormat="1" customHeight="1" s="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Cuenta</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>LineaNegocio</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>NuevoSaldo</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Pais</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Ajuste1</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Ajuste2</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" ht="14.25">
-      <c r="A2" s="15"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
+    <row r="2" ht="14.25" customFormat="1" customHeight="1" s="1">
+      <c r="A2" s="15" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="9" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="8" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J501" xr:uid="{00000000-0002-0000-0300-000000000000}">
+  <dataValidations count="3">
+    <dataValidation sqref="J2:J501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>Lista_Ajuste1</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K501" xr:uid="{00000000-0002-0000-0300-000001000000}">
+    <dataValidation sqref="K2:K501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>Lista_Ajuste2</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation sqref="G2:G501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lista_Pais</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF583AFF"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="2" width="13" style="12" customWidth="1"/>
-    <col min="3" max="3" width="15" style="12" customWidth="1"/>
-    <col min="4" max="7" width="13" style="12" customWidth="1"/>
-    <col min="8" max="16384" width="10.85546875" style="12"/>
+    <col width="13" customWidth="1" style="12" min="1" max="2"/>
+    <col width="15" customWidth="1" style="12" min="3" max="3"/>
+    <col width="13" customWidth="1" style="12" min="4" max="7"/>
+    <col width="10.85546875" customWidth="1" style="12" min="8" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>9</v>
+    <row r="1" ht="19.5" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Cuenta</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Presupuesto</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Pais</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="16" t="n"/>
+      <c r="B2" s="16" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E2:E501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lista_Pais</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF583AFF"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8334"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="11.25"/>
   <cols>
-    <col min="1" max="1" width="13" style="18" customWidth="1"/>
-    <col min="2" max="2" width="15" style="18" customWidth="1"/>
-    <col min="3" max="3" width="13" style="18" customWidth="1"/>
-    <col min="4" max="4" width="16" style="18" customWidth="1"/>
-    <col min="5" max="5" width="13" style="19" customWidth="1"/>
-    <col min="6" max="11" width="13" style="18" customWidth="1"/>
-    <col min="12" max="16384" width="10.5703125" style="18"/>
+    <col width="13" customWidth="1" style="18" min="1" max="1"/>
+    <col width="15" customWidth="1" style="18" min="2" max="2"/>
+    <col width="13" customWidth="1" style="18" min="3" max="3"/>
+    <col width="16" customWidth="1" style="18" min="4" max="4"/>
+    <col width="13" customWidth="1" style="19" min="5" max="5"/>
+    <col width="13" customWidth="1" style="18" min="6" max="11"/>
+    <col width="10.5703125" customWidth="1" style="18" min="12" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="20" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>14</v>
+    <row r="1" ht="19.5" customFormat="1" customHeight="1" s="20">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Cuenta</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>LineaNegocio</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Saldo</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Pais</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Ajuste1</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Ajuste2</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="12.75" customHeight="1">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
+    <row r="2" ht="12.75" customHeight="1">
+      <c r="A2" s="8" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="9" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="8" t="n"/>
     </row>
-    <row r="3" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="4" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="5" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="6" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="7" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="8" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="9" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="10" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="11" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="12" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="13" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="14" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="15" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="16" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="3" ht="12.75" customHeight="1"/>
+    <row r="4" ht="12.75" customHeight="1"/>
+    <row r="5" ht="12.75" customHeight="1"/>
+    <row r="6" ht="12.75" customHeight="1"/>
+    <row r="7" ht="12.75" customHeight="1"/>
+    <row r="8" ht="12.75" customHeight="1"/>
+    <row r="9" ht="12.75" customHeight="1"/>
+    <row r="10" ht="12.75" customHeight="1"/>
+    <row r="11" ht="12.75" customHeight="1"/>
+    <row r="12" ht="12.75" customHeight="1"/>
+    <row r="13" ht="12.75" customHeight="1"/>
+    <row r="14" ht="12.75" customHeight="1"/>
+    <row r="15" ht="12.75" customHeight="1"/>
+    <row r="16" ht="12.75" customHeight="1"/>
     <row r="17" ht="12.75" customHeight="1"/>
     <row r="18" ht="12.75" customHeight="1"/>
     <row r="19" ht="12.75" customHeight="1"/>
@@ -10279,105 +10459,132 @@
     <row r="8333" ht="14.25" customHeight="1"/>
     <row r="8334" ht="14.25" customHeight="1"/>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J501" xr:uid="{00000000-0002-0000-0500-000000000000}">
+  <dataValidations count="3">
+    <dataValidation sqref="J2:J501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>Lista_Ajuste1</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K501" xr:uid="{00000000-0002-0000-0500-000001000000}">
+    <dataValidation sqref="K2:K501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>Lista_Ajuste2</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation sqref="G2:G501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lista_Pais</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF583AFF"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11597"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="11.25"/>
   <cols>
-    <col min="1" max="1" width="13" style="21" customWidth="1"/>
-    <col min="2" max="2" width="15" style="21" customWidth="1"/>
-    <col min="3" max="3" width="13" style="21" customWidth="1"/>
-    <col min="4" max="4" width="16" style="21" customWidth="1"/>
-    <col min="5" max="5" width="13" style="22" customWidth="1"/>
-    <col min="6" max="10" width="13" style="21" customWidth="1"/>
-    <col min="11" max="11" width="13" style="18" customWidth="1"/>
-    <col min="12" max="16384" width="10.5703125" style="21"/>
+    <col width="13" customWidth="1" style="21" min="1" max="1"/>
+    <col width="15" customWidth="1" style="21" min="2" max="2"/>
+    <col width="13" customWidth="1" style="21" min="3" max="3"/>
+    <col width="16" customWidth="1" style="21" min="4" max="4"/>
+    <col width="13" customWidth="1" style="22" min="5" max="5"/>
+    <col width="13" customWidth="1" style="21" min="6" max="10"/>
+    <col width="13" customWidth="1" style="18" min="11" max="11"/>
+    <col width="10.5703125" customWidth="1" style="21" min="12" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="23" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>14</v>
+    <row r="1" ht="19.5" customFormat="1" customHeight="1" s="23">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Cuenta</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>LineaNegocio</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Saldo</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Pais</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Ajuste1</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>Ajuste2</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="12.75" customHeight="1">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
+    <row r="2" ht="12.75" customHeight="1">
+      <c r="A2" s="8" t="n"/>
+      <c r="B2" s="8" t="n"/>
+      <c r="C2" s="8" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="9" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="8" t="n"/>
+      <c r="K2" s="8" t="n"/>
     </row>
-    <row r="3" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="4" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="5" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="6" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="7" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="8" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="9" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="10" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="11" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="12" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="13" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="14" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="15" spans="1:11" ht="12.75" customHeight="1"/>
-    <row r="16" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="3" ht="12.75" customHeight="1"/>
+    <row r="4" ht="12.75" customHeight="1"/>
+    <row r="5" ht="12.75" customHeight="1"/>
+    <row r="6" ht="12.75" customHeight="1"/>
+    <row r="7" ht="12.75" customHeight="1"/>
+    <row r="8" ht="12.75" customHeight="1"/>
+    <row r="9" ht="12.75" customHeight="1"/>
+    <row r="10" ht="12.75" customHeight="1"/>
+    <row r="11" ht="12.75" customHeight="1"/>
+    <row r="12" ht="12.75" customHeight="1"/>
+    <row r="13" ht="12.75" customHeight="1"/>
+    <row r="14" ht="12.75" customHeight="1"/>
+    <row r="15" ht="12.75" customHeight="1"/>
+    <row r="16" ht="12.75" customHeight="1"/>
     <row r="17" ht="12.75" customHeight="1"/>
     <row r="18" ht="12.75" customHeight="1"/>
     <row r="19" ht="12.75" customHeight="1"/>
@@ -21960,1011 +22167,1178 @@
     <row r="11596" ht="15" customHeight="1"/>
     <row r="11597" ht="15" customHeight="1"/>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J501" xr:uid="{00000000-0002-0000-0600-000000000000}">
+  <dataValidations count="3">
+    <dataValidation sqref="J2:J501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>Lista_Ajuste1</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K501" xr:uid="{00000000-0002-0000-0600-000001000000}">
+    <dataValidation sqref="K2:K501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>Lista_Ajuste2</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation sqref="G2:G501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>Lista_Pais</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF583AFF"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="13" style="24" customWidth="1"/>
-    <col min="4" max="5" width="13" customWidth="1"/>
+    <col width="13" customWidth="1" min="1" max="2"/>
+    <col width="13" customWidth="1" style="24" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19.5" customHeight="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" ht="19.5" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Cuenta</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="25" t="n">
+        <v>410</v>
+      </c>
+      <c r="B2" s="25" t="inlineStr">
+        <is>
+          <t>Ingresos</t>
+        </is>
+      </c>
+      <c r="C2" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="D2" s="27" t="n"/>
+      <c r="E2" s="27" t="n"/>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A2" s="25">
-        <v>410</v>
-      </c>
-      <c r="B2" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="26">
+    <row r="3">
+      <c r="A3" s="8" t="n">
+        <v>51050</v>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Gastos de personal</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="8">
-        <v>51050</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="9">
+    <row r="4">
+      <c r="A4" s="25" t="n">
+        <v>51100</v>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>Honorarios</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
+      <c r="D4" s="27" t="n"/>
+      <c r="E4" s="27" t="n"/>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="25">
-        <v>51100</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="26">
+    <row r="5">
+      <c r="A5" s="8" t="n">
+        <v>51150</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Impuestos</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="8">
-        <v>51150</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="9">
+    <row r="6">
+      <c r="A6" s="25" t="n">
+        <v>51200</v>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>Arrendamientos</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
+      <c r="D6" s="27" t="n"/>
+      <c r="E6" s="27" t="n"/>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="25">
-        <v>51200</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="26">
+    <row r="7">
+      <c r="A7" s="8" t="n">
+        <v>51250</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Contribuciones y afiliaciones</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="8">
-        <v>51250</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="9">
+    <row r="8">
+      <c r="A8" s="25" t="n">
+        <v>51300</v>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>Seguros</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
+      <c r="D8" s="27" t="n"/>
+      <c r="E8" s="27" t="n"/>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="25">
-        <v>51300</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="26">
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>51350</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="8">
-        <v>51350</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="9">
+    <row r="10">
+      <c r="A10" s="25" t="n">
+        <v>51400</v>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>Gastos legales</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
+      <c r="D10" s="27" t="n"/>
+      <c r="E10" s="27" t="n"/>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="25">
-        <v>51400</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="26">
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>51450</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Mantenimiento y reparaciones</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="8">
-        <v>51450</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="9">
+    <row r="12">
+      <c r="A12" s="25" t="n">
+        <v>51500</v>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>Adecuación e instalación</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
+      <c r="D12" s="27" t="n"/>
+      <c r="E12" s="27" t="n"/>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="25">
-        <v>51500</v>
-      </c>
-      <c r="B12" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="26">
+    <row r="13">
+      <c r="A13" s="8" t="n">
+        <v>51550</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Gastos de viaje</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="8">
-        <v>51550</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="9">
+    <row r="14">
+      <c r="A14" s="25" t="n">
+        <v>51950</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="27" t="n"/>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="25">
-        <v>51950</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="26">
+    <row r="15">
+      <c r="A15" s="8" t="n">
+        <v>5199010</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Provisión Cartera</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="8">
-        <v>5199010</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="9">
+    <row r="16">
+      <c r="A16" s="25" t="n">
+        <v>5199020</v>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>Provisión Inventario</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
+      <c r="D16" s="27" t="n"/>
+      <c r="E16" s="27" t="n"/>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="25">
-        <v>5199020</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="26">
+    <row r="17">
+      <c r="A17" s="8" t="n">
+        <v>52050</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Gastos de personal</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="8">
-        <v>52050</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="9">
+    <row r="18">
+      <c r="A18" s="25" t="n">
+        <v>52100</v>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>Honorarios</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
+      <c r="D18" s="27" t="n"/>
+      <c r="E18" s="27" t="n"/>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="25">
-        <v>52100</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="26">
+    <row r="19">
+      <c r="A19" s="8" t="n">
+        <v>52150</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Impuestos</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="8">
-        <v>52150</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="9">
+    <row r="20">
+      <c r="A20" s="25" t="n">
+        <v>52200</v>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>Arrendamientos</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="25">
-        <v>52200</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="26">
+    <row r="21">
+      <c r="A21" s="8" t="n">
+        <v>52250</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Contribuciones y afiliaciones</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="8">
-        <v>52250</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="9">
+    <row r="22">
+      <c r="A22" s="25" t="n">
+        <v>52300</v>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>Seguros</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="27" t="n"/>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="25">
-        <v>52300</v>
-      </c>
-      <c r="B22" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="26">
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>52350</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="8">
-        <v>52350</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="9">
+    <row r="24">
+      <c r="A24" s="25" t="n">
+        <v>52400</v>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>Gastos legales</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="25">
-        <v>52400</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="26">
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>52450</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Mantenimiento y reparaciones</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="8">
-        <v>52450</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="9">
+    <row r="26">
+      <c r="A26" s="25" t="n">
+        <v>52500</v>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>Adecuación e instalación</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="27" t="n"/>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="25">
-        <v>52500</v>
-      </c>
-      <c r="B26" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="26">
+    <row r="27">
+      <c r="A27" s="8" t="n">
+        <v>52550</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Gastos de viaje</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="8">
-        <v>52550</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="9">
+    <row r="28">
+      <c r="A28" s="25" t="n">
+        <v>52950</v>
+      </c>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
+      <c r="D28" s="27" t="n"/>
+      <c r="E28" s="27" t="n"/>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="25">
-        <v>52950</v>
-      </c>
-      <c r="B28" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="26">
+    <row r="29">
+      <c r="A29" s="8" t="n">
+        <v>5299010</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Provisión Cartera</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="8">
-        <v>5299010</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="9">
+    <row r="30">
+      <c r="A30" s="25" t="n">
+        <v>5299020</v>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>Provisión Inventario</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
+      <c r="D30" s="27" t="n"/>
+      <c r="E30" s="27" t="n"/>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="25">
-        <v>5299020</v>
-      </c>
-      <c r="B30" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="26">
+    <row r="31">
+      <c r="A31" s="8" t="n">
+        <v>42050</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Otras ventas</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="8">
-        <v>42050</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31" s="9">
+    <row r="32">
+      <c r="A32" s="25" t="n">
+        <v>42500</v>
+      </c>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>Recuperaciones</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
+      <c r="D32" s="27" t="n"/>
+      <c r="E32" s="27" t="n"/>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="25">
-        <v>42500</v>
-      </c>
-      <c r="B32" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C32" s="26">
+    <row r="33">
+      <c r="A33" s="8" t="n">
+        <v>42150</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
     </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="8">
-        <v>42150</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C33" s="9">
+    <row r="34">
+      <c r="A34" s="25" t="n">
+        <v>53100</v>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>Pérdida en venta y retiro de bienes</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
+      <c r="D34" s="27" t="n"/>
+      <c r="E34" s="27" t="n"/>
     </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="25">
-        <v>53100</v>
-      </c>
-      <c r="B34" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C34" s="26">
+    <row r="35">
+      <c r="A35" s="8" t="n">
+        <v>53150</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Gastos extraordinarios</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
     </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="8">
-        <v>53150</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C35" s="9">
+    <row r="36">
+      <c r="A36" s="25" t="n">
+        <v>53130</v>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>Gastos diversos</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="25">
-        <v>53130</v>
-      </c>
-      <c r="B36" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36" s="26">
-        <v>0</v>
-      </c>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
+      <c r="D36" s="27" t="n"/>
+      <c r="E36" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF583AFF"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="13" style="24" customWidth="1"/>
-    <col min="4" max="5" width="13" customWidth="1"/>
+    <col width="13" customWidth="1" min="1" max="2"/>
+    <col width="13" customWidth="1" style="24" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19.5" customHeight="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" ht="19.5" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Cuenta</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="25" t="n">
+        <v>410</v>
+      </c>
+      <c r="B2" s="25" t="inlineStr">
+        <is>
+          <t>Ingresos</t>
+        </is>
+      </c>
+      <c r="C2" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="D2" s="27" t="n"/>
+      <c r="E2" s="27" t="n"/>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A2" s="25">
-        <v>410</v>
-      </c>
-      <c r="B2" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="26">
+    <row r="3">
+      <c r="A3" s="8" t="n">
+        <v>51050</v>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Gastos de personal</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="8">
-        <v>51050</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="9">
+    <row r="4">
+      <c r="A4" s="25" t="n">
+        <v>51100</v>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>Honorarios</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
+      <c r="D4" s="27" t="n"/>
+      <c r="E4" s="27" t="n"/>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="25">
-        <v>51100</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="26">
+    <row r="5">
+      <c r="A5" s="8" t="n">
+        <v>51150</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Impuestos</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="8">
-        <v>51150</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="9">
+    <row r="6">
+      <c r="A6" s="25" t="n">
+        <v>51200</v>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>Arrendamientos</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
+      <c r="D6" s="27" t="n"/>
+      <c r="E6" s="27" t="n"/>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="25">
-        <v>51200</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="26">
+    <row r="7">
+      <c r="A7" s="8" t="n">
+        <v>51250</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Contribuciones y afiliaciones</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="8">
-        <v>51250</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="9">
+    <row r="8">
+      <c r="A8" s="25" t="n">
+        <v>51300</v>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>Seguros</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
+      <c r="D8" s="27" t="n"/>
+      <c r="E8" s="27" t="n"/>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="25">
-        <v>51300</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="26">
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>51350</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="8">
-        <v>51350</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="9">
+    <row r="10">
+      <c r="A10" s="25" t="n">
+        <v>51400</v>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>Gastos legales</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
+      <c r="D10" s="27" t="n"/>
+      <c r="E10" s="27" t="n"/>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="25">
-        <v>51400</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="26">
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>51450</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Mantenimiento y reparaciones</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="8">
-        <v>51450</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="9">
+    <row r="12">
+      <c r="A12" s="25" t="n">
+        <v>51500</v>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>Adecuación e instalación</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
+      <c r="D12" s="27" t="n"/>
+      <c r="E12" s="27" t="n"/>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="25">
-        <v>51500</v>
-      </c>
-      <c r="B12" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="26">
+    <row r="13">
+      <c r="A13" s="8" t="n">
+        <v>51550</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Gastos de viaje</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="8">
-        <v>51550</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="9">
+    <row r="14">
+      <c r="A14" s="25" t="n">
+        <v>51950</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="27" t="n"/>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="25">
-        <v>51950</v>
-      </c>
-      <c r="B14" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="26">
+    <row r="15">
+      <c r="A15" s="8" t="n">
+        <v>5199010</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Provisión Cartera</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="8">
-        <v>5199010</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="9">
+    <row r="16">
+      <c r="A16" s="25" t="n">
+        <v>5199020</v>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>Provisión Inventario</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
+      <c r="D16" s="27" t="n"/>
+      <c r="E16" s="27" t="n"/>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="25">
-        <v>5199020</v>
-      </c>
-      <c r="B16" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="26">
+    <row r="17">
+      <c r="A17" s="8" t="n">
+        <v>52050</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Gastos de personal</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="8">
-        <v>52050</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="9">
+    <row r="18">
+      <c r="A18" s="25" t="n">
+        <v>52100</v>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>Honorarios</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
+      <c r="D18" s="27" t="n"/>
+      <c r="E18" s="27" t="n"/>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="25">
-        <v>52100</v>
-      </c>
-      <c r="B18" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="26">
+    <row r="19">
+      <c r="A19" s="8" t="n">
+        <v>52150</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Impuestos</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="8">
-        <v>52150</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="9">
+    <row r="20">
+      <c r="A20" s="25" t="n">
+        <v>52200</v>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>Arrendamientos</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="25">
-        <v>52200</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="26">
+    <row r="21">
+      <c r="A21" s="8" t="n">
+        <v>52250</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Contribuciones y afiliaciones</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="8">
-        <v>52250</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="9">
+    <row r="22">
+      <c r="A22" s="25" t="n">
+        <v>52300</v>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>Seguros</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="27" t="n"/>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="25">
-        <v>52300</v>
-      </c>
-      <c r="B22" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="26">
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>52350</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="8">
-        <v>52350</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="9">
+    <row r="24">
+      <c r="A24" s="25" t="n">
+        <v>52400</v>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>Gastos legales</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="25">
-        <v>52400</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="26">
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>52450</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Mantenimiento y reparaciones</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="8">
-        <v>52450</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="9">
+    <row r="26">
+      <c r="A26" s="25" t="n">
+        <v>52500</v>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>Adecuación e instalación</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="27" t="n"/>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="25">
-        <v>52500</v>
-      </c>
-      <c r="B26" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="26">
+    <row r="27">
+      <c r="A27" s="8" t="n">
+        <v>52550</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Gastos de viaje</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="8">
-        <v>52550</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="9">
+    <row r="28">
+      <c r="A28" s="25" t="n">
+        <v>52950</v>
+      </c>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
+      <c r="D28" s="27" t="n"/>
+      <c r="E28" s="27" t="n"/>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="25">
-        <v>52950</v>
-      </c>
-      <c r="B28" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="26">
+    <row r="29">
+      <c r="A29" s="8" t="n">
+        <v>5299010</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Provisión Cartera</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="8">
-        <v>5299010</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="9">
+    <row r="30">
+      <c r="A30" s="25" t="n">
+        <v>5299020</v>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>Provisión Inventario</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
+      <c r="D30" s="27" t="n"/>
+      <c r="E30" s="27" t="n"/>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="25">
-        <v>5299020</v>
-      </c>
-      <c r="B30" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="26">
+    <row r="31">
+      <c r="A31" s="8" t="n">
+        <v>42050</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Otras ventas</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="8">
-        <v>42050</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31" s="9">
+    <row r="32">
+      <c r="A32" s="25" t="n">
+        <v>42500</v>
+      </c>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>Recuperaciones</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
+      <c r="D32" s="27" t="n"/>
+      <c r="E32" s="27" t="n"/>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="25">
-        <v>42500</v>
-      </c>
-      <c r="B32" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C32" s="26">
+    <row r="33">
+      <c r="A33" s="8" t="n">
+        <v>42150</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Diversos</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
     </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="8">
-        <v>42150</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C33" s="9">
+    <row r="34">
+      <c r="A34" s="25" t="n">
+        <v>53100</v>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>Pérdida en venta y retiro de bienes</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
+      <c r="D34" s="27" t="n"/>
+      <c r="E34" s="27" t="n"/>
     </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="25">
-        <v>53100</v>
-      </c>
-      <c r="B34" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C34" s="26">
+    <row r="35">
+      <c r="A35" s="8" t="n">
+        <v>53150</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Gastos extraordinarios</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
     </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="8">
-        <v>53150</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C35" s="9">
+    <row r="36">
+      <c r="A36" s="25" t="n">
+        <v>53130</v>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>Gastos diversos</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="25">
-        <v>53130</v>
-      </c>
-      <c r="B36" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36" s="26">
-        <v>0</v>
-      </c>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
+      <c r="D36" s="27" t="n"/>
+      <c r="E36" s="27" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Assets/Plantillas/PlantillaBUFINS.xlsx
+++ b/Assets/Plantillas/PlantillaBUFINS.xlsx
@@ -1,21 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\omara_\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3FC022C-8F91-419A-831B-23016672EBFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="4" activeTab="8" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_BalancePrueba" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_CteYnoCte" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_PYGDetallado" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_PYGDetalladoConAjuste" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_PresupuestoBalance" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_PptoPYGDetallado" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_PptoPYGDetalladoConAjuste" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_PCH" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_EjecPCH" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="10" state="hidden" r:id="rId10"/>
+    <sheet name="Z_BalancePrueba" sheetId="1" r:id="rId1"/>
+    <sheet name="Z_CteYnoCte" sheetId="2" r:id="rId2"/>
+    <sheet name="Z_PYGDetallado" sheetId="3" r:id="rId3"/>
+    <sheet name="Z_PYGDetalladoConAjuste" sheetId="4" r:id="rId4"/>
+    <sheet name="Z_PresupuestoBalance" sheetId="5" r:id="rId5"/>
+    <sheet name="Z_PptoPYGDetallado" sheetId="6" r:id="rId6"/>
+    <sheet name="Z_PptoPYGDetalladoConAjuste" sheetId="7" r:id="rId7"/>
+    <sheet name="Z_PCH" sheetId="8" r:id="rId8"/>
+    <sheet name="Z_EjecPCH" sheetId="9" r:id="rId9"/>
+    <sheet name="Datos" sheetId="10" state="hidden" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="Lista_AcPa">Datos!$C$2:$C$5</definedName>
@@ -23,129 +30,621 @@
     <definedName name="Lista_Ajuste2">Datos!$B$2:$B$4</definedName>
     <definedName name="Lista_Pais">Datos!$D$2:$D$36</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    El  Z_BalancePrueba debe estar a 1, 2, 4 y 6 dígitos del PUC</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Las cuentas Z_CteYnoCte deben estar a 4 dígitos del PUC. Solo debe incluir las cuentas de balance que tienen porción corriente y no corriente e incluir el movimiento completo de las cuentas. </t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Las cuentas Z_PYGDetallado deben estar a 6 dígitos del PUC</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Las cuentas Z_PYGDetalladoConAjuste deben estar a 6 dígitos del PUC</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Las cuentas Z_PresupuestoBalance deben estar a 1, 2, 4 y 6 dígitos del PUC</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Las cuentas Z_PptoPYGDetallado deben estar a 6 dígitos del PUC</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Las cuentas Z_PptoPYGDetalladoConAjuste deben estar a 6 dígitos del PUC</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Las cuentas Z_PCH son las que se detallan en esta plantilla</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Las cuentas Z_PCH son las que se detallan en esta plantilla</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="83">
+  <si>
+    <t>Cuenta</t>
+  </si>
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Año</t>
+  </si>
+  <si>
+    <t>Mes</t>
+  </si>
+  <si>
+    <t>Ingresos</t>
+  </si>
+  <si>
+    <t>Gastos de personal</t>
+  </si>
+  <si>
+    <t>Honorarios</t>
+  </si>
+  <si>
+    <t>Impuestos</t>
+  </si>
+  <si>
+    <t>Arrendamientos</t>
+  </si>
+  <si>
+    <t>Contribuciones y afiliaciones</t>
+  </si>
+  <si>
+    <t>Seguros</t>
+  </si>
+  <si>
+    <t>Servicios</t>
+  </si>
+  <si>
+    <t>Gastos legales</t>
+  </si>
+  <si>
+    <t>Mantenimiento y reparaciones</t>
+  </si>
+  <si>
+    <t>Adecuación e instalación</t>
+  </si>
+  <si>
+    <t>Gastos de viaje</t>
+  </si>
+  <si>
+    <t>Diversos</t>
+  </si>
+  <si>
+    <t>Provisión Cartera</t>
+  </si>
+  <si>
+    <t>Provisión Inventario</t>
+  </si>
+  <si>
+    <t>Otras ventas</t>
+  </si>
+  <si>
+    <t>Recuperaciones</t>
+  </si>
+  <si>
+    <t>Pérdida en venta y retiro de bienes</t>
+  </si>
+  <si>
+    <t>Gastos extraordinarios</t>
+  </si>
+  <si>
+    <t>Gastos diversos</t>
+  </si>
+  <si>
+    <t>Descripcion</t>
+  </si>
+  <si>
+    <t>SaldoAnterior</t>
+  </si>
+  <si>
+    <t>Debito</t>
+  </si>
+  <si>
+    <t>Credito</t>
+  </si>
+  <si>
+    <t>NuevoSaldo</t>
+  </si>
+  <si>
+    <t>Empresa</t>
+  </si>
+  <si>
+    <t>Pais</t>
+  </si>
+  <si>
+    <t>AcPa</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>LineaNegocio</t>
+  </si>
+  <si>
+    <t>Ajuste1</t>
+  </si>
+  <si>
+    <t>Ajuste2</t>
+  </si>
+  <si>
+    <t>Presupuesto</t>
+  </si>
+  <si>
+    <t>Saldo</t>
+  </si>
+  <si>
+    <t>Ebitda</t>
+  </si>
+  <si>
+    <t>GASTOS FIJOS</t>
+  </si>
+  <si>
+    <t>ACTIVO CORRIENTE</t>
+  </si>
+  <si>
+    <t>Antigua y Barbuda</t>
+  </si>
+  <si>
+    <t>No Ebitda</t>
+  </si>
+  <si>
+    <t>VARIABLES</t>
+  </si>
+  <si>
+    <t>ACTIVO NO CORRIENTE</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>OTROS GASTOS</t>
+  </si>
+  <si>
+    <t>PASIVO NO CORRIENTE</t>
+  </si>
+  <si>
+    <t>Bahamas</t>
+  </si>
+  <si>
+    <t>PASIVO CORRIENTE</t>
+  </si>
+  <si>
+    <t>Barbados</t>
+  </si>
+  <si>
+    <t>Belice</t>
+  </si>
+  <si>
+    <t>Bolivia</t>
+  </si>
+  <si>
+    <t>Brasil</t>
+  </si>
+  <si>
+    <t>Canadá</t>
+  </si>
+  <si>
+    <t>Chile</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>Costa Rica</t>
+  </si>
+  <si>
+    <t>Cuba</t>
+  </si>
+  <si>
+    <t>Dominica</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>El Salvador</t>
+  </si>
+  <si>
+    <t>Estados Unidos</t>
+  </si>
+  <si>
+    <t>Granada</t>
+  </si>
+  <si>
+    <t>Guatemala</t>
+  </si>
+  <si>
+    <t>Guyana</t>
+  </si>
+  <si>
+    <t>Haití</t>
+  </si>
+  <si>
+    <t>Honduras</t>
+  </si>
+  <si>
+    <t>Jamaica</t>
+  </si>
+  <si>
+    <t>México</t>
+  </si>
+  <si>
+    <t>Nicaragua</t>
+  </si>
+  <si>
+    <t>Panamá</t>
+  </si>
+  <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
+    <t>Perú</t>
+  </si>
+  <si>
+    <t>República Dominicana</t>
+  </si>
+  <si>
+    <t>San Cristóbal y Nieves</t>
+  </si>
+  <si>
+    <t>San Vicente y las Granadinas</t>
+  </si>
+  <si>
+    <t>Santa Lucía</t>
+  </si>
+  <si>
+    <t>Trinidad y Tobago</t>
+  </si>
+  <si>
+    <t>Uruguay</t>
+  </si>
+  <si>
+    <t>Venezuela</t>
+  </si>
+  <si>
+    <t>Surinam</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* \-??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * \-??_ ;_ @_ "/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* \-??\ _€_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* \-_);_(@_)"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-      <sz val="10"/>
+      <charset val="1"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Geomanist Light"/>
+      <family val="2"/>
       <charset val="1"/>
-      <family val="2"/>
-      <color theme="10"/>
-      <sz val="11"/>
-      <u val="single"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
       <charset val="1"/>
-      <family val="2"/>
-      <sz val="10"/>
     </font>
     <font>
-      <name val="Geomanist Light"/>
+      <sz val="10"/>
+      <name val="Cyntho"/>
       <charset val="1"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
-      <name val="Tahoma"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF01E1D7"/>
+      <name val="Cyntho"/>
       <charset val="1"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="8"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
       <name val="Cyntho"/>
       <charset val="1"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Cyntho"/>
       <charset val="1"/>
-      <b val="1"/>
-      <color rgb="FF01E1D7"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Cyntho"/>
       <charset val="1"/>
-      <b val="1"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Cyntho"/>
       <charset val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="8"/>
       <name val="Cyntho"/>
       <charset val="1"/>
-      <color theme="1"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Cyntho"/>
       <charset val="1"/>
-      <color theme="1"/>
-      <sz val="8"/>
     </font>
     <font>
-      <name val="Cyntho"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="2"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Cyntho"/>
-      <charset val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -207,162 +706,151 @@
     </border>
   </borders>
   <cellStyleXfs count="184">
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="49" fontId="16" fillId="2" borderId="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="49" fontId="15" fillId="2" borderId="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0"/>
@@ -373,263 +861,275 @@
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="30">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="9" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="9" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="9" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="9" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="9" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="184">
+    <cellStyle name="Comma 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Estilo 1" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Hipervínculo 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Millares" xfId="1" builtinId="3"/>
+    <cellStyle name="Millares [0] 2" xfId="145" xr:uid="{00000000-0005-0000-0000-000091000000}"/>
+    <cellStyle name="Millares [0] 2 2" xfId="146" xr:uid="{00000000-0005-0000-0000-000092000000}"/>
+    <cellStyle name="Millares [0] 2 2 2" xfId="147" xr:uid="{00000000-0005-0000-0000-000093000000}"/>
+    <cellStyle name="Millares [0] 2 2 2 2" xfId="148" xr:uid="{00000000-0005-0000-0000-000094000000}"/>
+    <cellStyle name="Millares [0] 2 2 3" xfId="149" xr:uid="{00000000-0005-0000-0000-000095000000}"/>
+    <cellStyle name="Millares [0] 2 2 4" xfId="150" xr:uid="{00000000-0005-0000-0000-000096000000}"/>
+    <cellStyle name="Millares [0] 2 3" xfId="151" xr:uid="{00000000-0005-0000-0000-000097000000}"/>
+    <cellStyle name="Millares [0] 2 3 2" xfId="152" xr:uid="{00000000-0005-0000-0000-000098000000}"/>
+    <cellStyle name="Millares [0] 2 4" xfId="153" xr:uid="{00000000-0005-0000-0000-000099000000}"/>
+    <cellStyle name="Millares [0] 2 5" xfId="154" xr:uid="{00000000-0005-0000-0000-00009A000000}"/>
+    <cellStyle name="Millares [0] 2 6" xfId="155" xr:uid="{00000000-0005-0000-0000-00009B000000}"/>
+    <cellStyle name="Millares [0] 3" xfId="156" xr:uid="{00000000-0005-0000-0000-00009C000000}"/>
+    <cellStyle name="Millares [0] 3 2" xfId="157" xr:uid="{00000000-0005-0000-0000-00009D000000}"/>
+    <cellStyle name="Millares [0] 3 2 2" xfId="158" xr:uid="{00000000-0005-0000-0000-00009E000000}"/>
+    <cellStyle name="Millares [0] 3 3" xfId="159" xr:uid="{00000000-0005-0000-0000-00009F000000}"/>
+    <cellStyle name="Millares [0] 3 3 2" xfId="160" xr:uid="{00000000-0005-0000-0000-0000A0000000}"/>
+    <cellStyle name="Millares [0] 3 4" xfId="161" xr:uid="{00000000-0005-0000-0000-0000A1000000}"/>
+    <cellStyle name="Millares [0] 3 5" xfId="162" xr:uid="{00000000-0005-0000-0000-0000A2000000}"/>
+    <cellStyle name="Millares [0] 3 6" xfId="163" xr:uid="{00000000-0005-0000-0000-0000A3000000}"/>
+    <cellStyle name="Millares [0] 4" xfId="164" xr:uid="{00000000-0005-0000-0000-0000A4000000}"/>
+    <cellStyle name="Millares [0] 4 2" xfId="165" xr:uid="{00000000-0005-0000-0000-0000A5000000}"/>
+    <cellStyle name="Millares [0] 5" xfId="166" xr:uid="{00000000-0005-0000-0000-0000A6000000}"/>
+    <cellStyle name="Millares [0] 6" xfId="167" xr:uid="{00000000-0005-0000-0000-0000A7000000}"/>
+    <cellStyle name="Millares 10" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Millares 10 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Millares 11" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Millares 11 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Millares 12" xfId="9" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Millares 12 2" xfId="10" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Millares 13" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Millares 13 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Millares 14" xfId="13" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Millares 14 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Millares 15" xfId="15" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Millares 15 2" xfId="16" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Millares 16" xfId="17" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Millares 16 2" xfId="18" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Millares 17" xfId="19" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Millares 17 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Millares 18" xfId="21" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Millares 18 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Millares 19" xfId="23" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="Millares 19 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="Millares 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="Millares 2 2" xfId="26" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="Millares 2 2 2" xfId="27" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="Millares 2 2 2 2" xfId="28" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="Millares 2 2 3" xfId="29" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="Millares 2 2 4" xfId="30" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="Millares 2 3" xfId="31" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="Millares 2 3 2" xfId="32" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="Millares 2 4" xfId="33" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
+    <cellStyle name="Millares 2 5" xfId="34" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="Millares 20" xfId="35" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
+    <cellStyle name="Millares 20 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
+    <cellStyle name="Millares 21" xfId="37" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="Millares 21 2" xfId="38" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="Millares 22" xfId="39" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="Millares 22 2" xfId="40" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
+    <cellStyle name="Millares 23" xfId="41" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
+    <cellStyle name="Millares 23 2" xfId="42" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
+    <cellStyle name="Millares 24" xfId="43" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
+    <cellStyle name="Millares 24 2" xfId="44" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
+    <cellStyle name="Millares 25" xfId="45" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
+    <cellStyle name="Millares 25 2" xfId="46" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="Millares 26" xfId="47" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
+    <cellStyle name="Millares 26 2" xfId="48" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
+    <cellStyle name="Millares 27" xfId="49" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="Millares 27 2" xfId="50" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="Millares 28" xfId="51" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="Millares 28 2" xfId="52" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="Millares 29" xfId="53" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="Millares 29 2" xfId="54" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="Millares 3" xfId="55" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="Millares 3 2" xfId="56" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="Millares 3 2 2" xfId="57" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="Millares 3 2 2 2" xfId="58" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="Millares 3 2 3" xfId="59" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="Millares 3 2 4" xfId="60" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
+    <cellStyle name="Millares 3 3" xfId="61" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
+    <cellStyle name="Millares 3 4" xfId="62" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
+    <cellStyle name="Millares 3 5" xfId="63" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
+    <cellStyle name="Millares 30" xfId="64" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
+    <cellStyle name="Millares 30 2" xfId="65" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
+    <cellStyle name="Millares 31" xfId="66" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
+    <cellStyle name="Millares 31 2" xfId="67" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
+    <cellStyle name="Millares 32" xfId="68" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
+    <cellStyle name="Millares 32 2" xfId="69" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
+    <cellStyle name="Millares 33" xfId="70" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
+    <cellStyle name="Millares 33 2" xfId="71" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
+    <cellStyle name="Millares 34" xfId="72" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
+    <cellStyle name="Millares 34 2" xfId="73" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
+    <cellStyle name="Millares 35" xfId="74" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
+    <cellStyle name="Millares 35 2" xfId="75" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
+    <cellStyle name="Millares 36" xfId="76" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
+    <cellStyle name="Millares 36 2" xfId="77" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
+    <cellStyle name="Millares 37" xfId="78" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
+    <cellStyle name="Millares 37 2" xfId="79" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
+    <cellStyle name="Millares 38" xfId="80" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
+    <cellStyle name="Millares 38 2" xfId="81" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
+    <cellStyle name="Millares 39" xfId="82" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
+    <cellStyle name="Millares 39 2" xfId="83" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
+    <cellStyle name="Millares 4" xfId="84" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
+    <cellStyle name="Millares 40" xfId="85" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
+    <cellStyle name="Millares 40 2" xfId="86" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
+    <cellStyle name="Millares 41" xfId="87" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
+    <cellStyle name="Millares 41 2" xfId="88" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
+    <cellStyle name="Millares 42" xfId="89" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
+    <cellStyle name="Millares 42 2" xfId="90" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
+    <cellStyle name="Millares 43" xfId="91" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
+    <cellStyle name="Millares 43 2" xfId="92" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
+    <cellStyle name="Millares 44" xfId="93" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
+    <cellStyle name="Millares 44 2" xfId="94" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
+    <cellStyle name="Millares 45" xfId="95" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
+    <cellStyle name="Millares 45 2" xfId="96" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
+    <cellStyle name="Millares 46" xfId="97" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
+    <cellStyle name="Millares 46 2" xfId="98" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
+    <cellStyle name="Millares 47" xfId="99" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
+    <cellStyle name="Millares 47 2" xfId="100" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
+    <cellStyle name="Millares 48" xfId="101" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
+    <cellStyle name="Millares 48 2" xfId="102" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
+    <cellStyle name="Millares 49" xfId="103" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
+    <cellStyle name="Millares 49 2" xfId="104" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
+    <cellStyle name="Millares 5" xfId="105" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
+    <cellStyle name="Millares 50" xfId="106" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
+    <cellStyle name="Millares 50 2" xfId="107" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
+    <cellStyle name="Millares 51" xfId="108" xr:uid="{00000000-0005-0000-0000-00006C000000}"/>
+    <cellStyle name="Millares 51 2" xfId="109" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
+    <cellStyle name="Millares 52" xfId="110" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
+    <cellStyle name="Millares 52 2" xfId="111" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
+    <cellStyle name="Millares 53" xfId="112" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
+    <cellStyle name="Millares 53 2" xfId="113" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
+    <cellStyle name="Millares 54" xfId="114" xr:uid="{00000000-0005-0000-0000-000072000000}"/>
+    <cellStyle name="Millares 54 2" xfId="115" xr:uid="{00000000-0005-0000-0000-000073000000}"/>
+    <cellStyle name="Millares 55" xfId="116" xr:uid="{00000000-0005-0000-0000-000074000000}"/>
+    <cellStyle name="Millares 55 2" xfId="117" xr:uid="{00000000-0005-0000-0000-000075000000}"/>
+    <cellStyle name="Millares 56" xfId="118" xr:uid="{00000000-0005-0000-0000-000076000000}"/>
+    <cellStyle name="Millares 56 2" xfId="119" xr:uid="{00000000-0005-0000-0000-000077000000}"/>
+    <cellStyle name="Millares 57" xfId="120" xr:uid="{00000000-0005-0000-0000-000078000000}"/>
+    <cellStyle name="Millares 58" xfId="121" xr:uid="{00000000-0005-0000-0000-000079000000}"/>
+    <cellStyle name="Millares 59" xfId="122" xr:uid="{00000000-0005-0000-0000-00007A000000}"/>
+    <cellStyle name="Millares 6" xfId="123" xr:uid="{00000000-0005-0000-0000-00007B000000}"/>
+    <cellStyle name="Millares 60" xfId="124" xr:uid="{00000000-0005-0000-0000-00007C000000}"/>
+    <cellStyle name="Millares 61" xfId="125" xr:uid="{00000000-0005-0000-0000-00007D000000}"/>
+    <cellStyle name="Millares 62" xfId="126" xr:uid="{00000000-0005-0000-0000-00007E000000}"/>
+    <cellStyle name="Millares 63" xfId="127" xr:uid="{00000000-0005-0000-0000-00007F000000}"/>
+    <cellStyle name="Millares 64" xfId="128" xr:uid="{00000000-0005-0000-0000-000080000000}"/>
+    <cellStyle name="Millares 65" xfId="129" xr:uid="{00000000-0005-0000-0000-000081000000}"/>
+    <cellStyle name="Millares 7" xfId="130" xr:uid="{00000000-0005-0000-0000-000082000000}"/>
+    <cellStyle name="Millares 7 2" xfId="131" xr:uid="{00000000-0005-0000-0000-000083000000}"/>
+    <cellStyle name="Millares 7 2 2" xfId="132" xr:uid="{00000000-0005-0000-0000-000084000000}"/>
+    <cellStyle name="Millares 7 3" xfId="133" xr:uid="{00000000-0005-0000-0000-000085000000}"/>
+    <cellStyle name="Millares 7 4" xfId="134" xr:uid="{00000000-0005-0000-0000-000086000000}"/>
+    <cellStyle name="Millares 8" xfId="135" xr:uid="{00000000-0005-0000-0000-000087000000}"/>
+    <cellStyle name="Millares 8 2" xfId="136" xr:uid="{00000000-0005-0000-0000-000088000000}"/>
+    <cellStyle name="Millares 8 2 2" xfId="137" xr:uid="{00000000-0005-0000-0000-000089000000}"/>
+    <cellStyle name="Millares 8 3" xfId="138" xr:uid="{00000000-0005-0000-0000-00008A000000}"/>
+    <cellStyle name="Millares 8 4" xfId="139" xr:uid="{00000000-0005-0000-0000-00008B000000}"/>
+    <cellStyle name="Millares 9" xfId="140" xr:uid="{00000000-0005-0000-0000-00008C000000}"/>
+    <cellStyle name="Millares 9 2" xfId="141" xr:uid="{00000000-0005-0000-0000-00008D000000}"/>
+    <cellStyle name="Millares 9 2 2" xfId="142" xr:uid="{00000000-0005-0000-0000-00008E000000}"/>
+    <cellStyle name="Millares 9 3" xfId="143" xr:uid="{00000000-0005-0000-0000-00008F000000}"/>
+    <cellStyle name="Millares 9 4" xfId="144" xr:uid="{00000000-0005-0000-0000-000090000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Millares" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma 2" xfId="2"/>
-    <cellStyle name="Estilo 1" xfId="3"/>
-    <cellStyle name="Hipervínculo 2" xfId="4"/>
-    <cellStyle name="Millares 10" xfId="5"/>
-    <cellStyle name="Millares 10 2" xfId="6"/>
-    <cellStyle name="Millares 11" xfId="7"/>
-    <cellStyle name="Millares 11 2" xfId="8"/>
-    <cellStyle name="Millares 12" xfId="9"/>
-    <cellStyle name="Millares 12 2" xfId="10"/>
-    <cellStyle name="Millares 13" xfId="11"/>
-    <cellStyle name="Millares 13 2" xfId="12"/>
-    <cellStyle name="Millares 14" xfId="13"/>
-    <cellStyle name="Millares 14 2" xfId="14"/>
-    <cellStyle name="Millares 15" xfId="15"/>
-    <cellStyle name="Millares 15 2" xfId="16"/>
-    <cellStyle name="Millares 16" xfId="17"/>
-    <cellStyle name="Millares 16 2" xfId="18"/>
-    <cellStyle name="Millares 17" xfId="19"/>
-    <cellStyle name="Millares 17 2" xfId="20"/>
-    <cellStyle name="Millares 18" xfId="21"/>
-    <cellStyle name="Millares 18 2" xfId="22"/>
-    <cellStyle name="Millares 19" xfId="23"/>
-    <cellStyle name="Millares 19 2" xfId="24"/>
-    <cellStyle name="Millares 2" xfId="25"/>
-    <cellStyle name="Millares 2 2" xfId="26"/>
-    <cellStyle name="Millares 2 2 2" xfId="27"/>
-    <cellStyle name="Millares 2 2 2 2" xfId="28"/>
-    <cellStyle name="Millares 2 2 3" xfId="29"/>
-    <cellStyle name="Millares 2 2 4" xfId="30"/>
-    <cellStyle name="Millares 2 3" xfId="31"/>
-    <cellStyle name="Millares 2 3 2" xfId="32"/>
-    <cellStyle name="Millares 2 4" xfId="33"/>
-    <cellStyle name="Millares 2 5" xfId="34"/>
-    <cellStyle name="Millares 20" xfId="35"/>
-    <cellStyle name="Millares 20 2" xfId="36"/>
-    <cellStyle name="Millares 21" xfId="37"/>
-    <cellStyle name="Millares 21 2" xfId="38"/>
-    <cellStyle name="Millares 22" xfId="39"/>
-    <cellStyle name="Millares 22 2" xfId="40"/>
-    <cellStyle name="Millares 23" xfId="41"/>
-    <cellStyle name="Millares 23 2" xfId="42"/>
-    <cellStyle name="Millares 24" xfId="43"/>
-    <cellStyle name="Millares 24 2" xfId="44"/>
-    <cellStyle name="Millares 25" xfId="45"/>
-    <cellStyle name="Millares 25 2" xfId="46"/>
-    <cellStyle name="Millares 26" xfId="47"/>
-    <cellStyle name="Millares 26 2" xfId="48"/>
-    <cellStyle name="Millares 27" xfId="49"/>
-    <cellStyle name="Millares 27 2" xfId="50"/>
-    <cellStyle name="Millares 28" xfId="51"/>
-    <cellStyle name="Millares 28 2" xfId="52"/>
-    <cellStyle name="Millares 29" xfId="53"/>
-    <cellStyle name="Millares 29 2" xfId="54"/>
-    <cellStyle name="Millares 3" xfId="55"/>
-    <cellStyle name="Millares 3 2" xfId="56"/>
-    <cellStyle name="Millares 3 2 2" xfId="57"/>
-    <cellStyle name="Millares 3 2 2 2" xfId="58"/>
-    <cellStyle name="Millares 3 2 3" xfId="59"/>
-    <cellStyle name="Millares 3 2 4" xfId="60"/>
-    <cellStyle name="Millares 3 3" xfId="61"/>
-    <cellStyle name="Millares 3 4" xfId="62"/>
-    <cellStyle name="Millares 3 5" xfId="63"/>
-    <cellStyle name="Millares 30" xfId="64"/>
-    <cellStyle name="Millares 30 2" xfId="65"/>
-    <cellStyle name="Millares 31" xfId="66"/>
-    <cellStyle name="Millares 31 2" xfId="67"/>
-    <cellStyle name="Millares 32" xfId="68"/>
-    <cellStyle name="Millares 32 2" xfId="69"/>
-    <cellStyle name="Millares 33" xfId="70"/>
-    <cellStyle name="Millares 33 2" xfId="71"/>
-    <cellStyle name="Millares 34" xfId="72"/>
-    <cellStyle name="Millares 34 2" xfId="73"/>
-    <cellStyle name="Millares 35" xfId="74"/>
-    <cellStyle name="Millares 35 2" xfId="75"/>
-    <cellStyle name="Millares 36" xfId="76"/>
-    <cellStyle name="Millares 36 2" xfId="77"/>
-    <cellStyle name="Millares 37" xfId="78"/>
-    <cellStyle name="Millares 37 2" xfId="79"/>
-    <cellStyle name="Millares 38" xfId="80"/>
-    <cellStyle name="Millares 38 2" xfId="81"/>
-    <cellStyle name="Millares 39" xfId="82"/>
-    <cellStyle name="Millares 39 2" xfId="83"/>
-    <cellStyle name="Millares 4" xfId="84"/>
-    <cellStyle name="Millares 40" xfId="85"/>
-    <cellStyle name="Millares 40 2" xfId="86"/>
-    <cellStyle name="Millares 41" xfId="87"/>
-    <cellStyle name="Millares 41 2" xfId="88"/>
-    <cellStyle name="Millares 42" xfId="89"/>
-    <cellStyle name="Millares 42 2" xfId="90"/>
-    <cellStyle name="Millares 43" xfId="91"/>
-    <cellStyle name="Millares 43 2" xfId="92"/>
-    <cellStyle name="Millares 44" xfId="93"/>
-    <cellStyle name="Millares 44 2" xfId="94"/>
-    <cellStyle name="Millares 45" xfId="95"/>
-    <cellStyle name="Millares 45 2" xfId="96"/>
-    <cellStyle name="Millares 46" xfId="97"/>
-    <cellStyle name="Millares 46 2" xfId="98"/>
-    <cellStyle name="Millares 47" xfId="99"/>
-    <cellStyle name="Millares 47 2" xfId="100"/>
-    <cellStyle name="Millares 48" xfId="101"/>
-    <cellStyle name="Millares 48 2" xfId="102"/>
-    <cellStyle name="Millares 49" xfId="103"/>
-    <cellStyle name="Millares 49 2" xfId="104"/>
-    <cellStyle name="Millares 5" xfId="105"/>
-    <cellStyle name="Millares 50" xfId="106"/>
-    <cellStyle name="Millares 50 2" xfId="107"/>
-    <cellStyle name="Millares 51" xfId="108"/>
-    <cellStyle name="Millares 51 2" xfId="109"/>
-    <cellStyle name="Millares 52" xfId="110"/>
-    <cellStyle name="Millares 52 2" xfId="111"/>
-    <cellStyle name="Millares 53" xfId="112"/>
-    <cellStyle name="Millares 53 2" xfId="113"/>
-    <cellStyle name="Millares 54" xfId="114"/>
-    <cellStyle name="Millares 54 2" xfId="115"/>
-    <cellStyle name="Millares 55" xfId="116"/>
-    <cellStyle name="Millares 55 2" xfId="117"/>
-    <cellStyle name="Millares 56" xfId="118"/>
-    <cellStyle name="Millares 56 2" xfId="119"/>
-    <cellStyle name="Millares 57" xfId="120"/>
-    <cellStyle name="Millares 58" xfId="121"/>
-    <cellStyle name="Millares 59" xfId="122"/>
-    <cellStyle name="Millares 6" xfId="123"/>
-    <cellStyle name="Millares 60" xfId="124"/>
-    <cellStyle name="Millares 61" xfId="125"/>
-    <cellStyle name="Millares 62" xfId="126"/>
-    <cellStyle name="Millares 63" xfId="127"/>
-    <cellStyle name="Millares 64" xfId="128"/>
-    <cellStyle name="Millares 65" xfId="129"/>
-    <cellStyle name="Millares 7" xfId="130"/>
-    <cellStyle name="Millares 7 2" xfId="131"/>
-    <cellStyle name="Millares 7 2 2" xfId="132"/>
-    <cellStyle name="Millares 7 3" xfId="133"/>
-    <cellStyle name="Millares 7 4" xfId="134"/>
-    <cellStyle name="Millares 8" xfId="135"/>
-    <cellStyle name="Millares 8 2" xfId="136"/>
-    <cellStyle name="Millares 8 2 2" xfId="137"/>
-    <cellStyle name="Millares 8 3" xfId="138"/>
-    <cellStyle name="Millares 8 4" xfId="139"/>
-    <cellStyle name="Millares 9" xfId="140"/>
-    <cellStyle name="Millares 9 2" xfId="141"/>
-    <cellStyle name="Millares 9 2 2" xfId="142"/>
-    <cellStyle name="Millares 9 3" xfId="143"/>
-    <cellStyle name="Millares 9 4" xfId="144"/>
-    <cellStyle name="Millares [0] 2" xfId="145"/>
-    <cellStyle name="Millares [0] 2 2" xfId="146"/>
-    <cellStyle name="Millares [0] 2 2 2" xfId="147"/>
-    <cellStyle name="Millares [0] 2 2 2 2" xfId="148"/>
-    <cellStyle name="Millares [0] 2 2 3" xfId="149"/>
-    <cellStyle name="Millares [0] 2 2 4" xfId="150"/>
-    <cellStyle name="Millares [0] 2 3" xfId="151"/>
-    <cellStyle name="Millares [0] 2 3 2" xfId="152"/>
-    <cellStyle name="Millares [0] 2 4" xfId="153"/>
-    <cellStyle name="Millares [0] 2 5" xfId="154"/>
-    <cellStyle name="Millares [0] 2 6" xfId="155"/>
-    <cellStyle name="Millares [0] 3" xfId="156"/>
-    <cellStyle name="Millares [0] 3 2" xfId="157"/>
-    <cellStyle name="Millares [0] 3 2 2" xfId="158"/>
-    <cellStyle name="Millares [0] 3 3" xfId="159"/>
-    <cellStyle name="Millares [0] 3 3 2" xfId="160"/>
-    <cellStyle name="Millares [0] 3 4" xfId="161"/>
-    <cellStyle name="Millares [0] 3 5" xfId="162"/>
-    <cellStyle name="Millares [0] 3 6" xfId="163"/>
-    <cellStyle name="Millares [0] 4" xfId="164"/>
-    <cellStyle name="Millares [0] 4 2" xfId="165"/>
-    <cellStyle name="Millares [0] 5" xfId="166"/>
-    <cellStyle name="Millares [0] 6" xfId="167"/>
-    <cellStyle name="Normal 10" xfId="168"/>
-    <cellStyle name="Normal 11" xfId="169"/>
-    <cellStyle name="Normal 2" xfId="170"/>
-    <cellStyle name="Normal 2 2" xfId="171"/>
-    <cellStyle name="Normal 2 3" xfId="172"/>
-    <cellStyle name="Normal 2 4" xfId="173"/>
-    <cellStyle name="Normal 2 5" xfId="174"/>
-    <cellStyle name="Normal 3" xfId="175"/>
-    <cellStyle name="Normal 4" xfId="176"/>
-    <cellStyle name="Normal 5" xfId="177"/>
-    <cellStyle name="Normal 6" xfId="178"/>
-    <cellStyle name="Normal 6 2" xfId="179"/>
-    <cellStyle name="Normal 7" xfId="180"/>
-    <cellStyle name="Normal 8" xfId="181"/>
-    <cellStyle name="Normal 9" xfId="182"/>
-    <cellStyle name="Porcentaje 2" xfId="183"/>
+    <cellStyle name="Normal 10" xfId="168" xr:uid="{00000000-0005-0000-0000-0000A8000000}"/>
+    <cellStyle name="Normal 11" xfId="169" xr:uid="{00000000-0005-0000-0000-0000A9000000}"/>
+    <cellStyle name="Normal 2" xfId="170" xr:uid="{00000000-0005-0000-0000-0000AA000000}"/>
+    <cellStyle name="Normal 2 2" xfId="171" xr:uid="{00000000-0005-0000-0000-0000AB000000}"/>
+    <cellStyle name="Normal 2 3" xfId="172" xr:uid="{00000000-0005-0000-0000-0000AC000000}"/>
+    <cellStyle name="Normal 2 4" xfId="173" xr:uid="{00000000-0005-0000-0000-0000AD000000}"/>
+    <cellStyle name="Normal 2 5" xfId="174" xr:uid="{00000000-0005-0000-0000-0000AE000000}"/>
+    <cellStyle name="Normal 3" xfId="175" xr:uid="{00000000-0005-0000-0000-0000AF000000}"/>
+    <cellStyle name="Normal 4" xfId="176" xr:uid="{00000000-0005-0000-0000-0000B0000000}"/>
+    <cellStyle name="Normal 5" xfId="177" xr:uid="{00000000-0005-0000-0000-0000B1000000}"/>
+    <cellStyle name="Normal 6" xfId="178" xr:uid="{00000000-0005-0000-0000-0000B2000000}"/>
+    <cellStyle name="Normal 6 2" xfId="179" xr:uid="{00000000-0005-0000-0000-0000B3000000}"/>
+    <cellStyle name="Normal 7" xfId="180" xr:uid="{00000000-0005-0000-0000-0000B4000000}"/>
+    <cellStyle name="Normal 8" xfId="181" xr:uid="{00000000-0005-0000-0000-0000B5000000}"/>
+    <cellStyle name="Normal 9" xfId="182" xr:uid="{00000000-0005-0000-0000-0000B6000000}"/>
+    <cellStyle name="Porcentaje 2" xfId="183" xr:uid="{00000000-0005-0000-0000-0000B7000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -699,322 +1199,168 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0">
-      <text>
-        <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
-    El  Z_BalancePrueba debe estar a 1, 2, 4 y 6 dígitos del PUC</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
-    Las cuentas Z_CteYnoCte deben estar a 4 dígitos del PUC. Solo debe incluir las cuentas de balance que tienen porción corriente y no corriente e incluir el movimiento completo de las cuentas. </t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0">
-      <text>
-        <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
-    Las cuentas Z_PYGDetallado deben estar a 6 dígitos del PUC</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0">
-      <text>
-        <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
-    Las cuentas Z_PYGDetalladoConAjuste deben estar a 6 dígitos del PUC</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0">
-      <text>
-        <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
-    Las cuentas Z_PresupuestoBalance deben estar a 1, 2, 4 y 6 dígitos del PUC</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0">
-      <text>
-        <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
-    Las cuentas Z_PptoPYGDetallado deben estar a 6 dígitos del PUC</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0">
-      <text>
-        <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
-    Las cuentas Z_PptoPYGDetalladoConAjuste deben estar a 6 dígitos del PUC</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment8.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0">
-      <text>
-        <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
-    Las cuentas Z_PCH son las que se detallan en esta plantilla</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment9.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Unknown Author</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0">
-      <text>
-        <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
-Comentario:
-    Las cuentas Z_PCH son las que se detallan en esta plantilla</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TablaBalance" displayName="TablaBalance" ref="A1:J2" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaBalance" displayName="TablaBalance" ref="A1:J2" totalsRowShown="0">
   <tableColumns count="10">
-    <tableColumn id="1" name="Cuenta"/>
-    <tableColumn id="2" name="Descripcion"/>
-    <tableColumn id="3" name="SaldoAnterior"/>
-    <tableColumn id="4" name="Debito"/>
-    <tableColumn id="5" name="Credito"/>
-    <tableColumn id="6" name="NuevoSaldo"/>
-    <tableColumn id="7" name="Empresa"/>
-    <tableColumn id="8" name="Pais"/>
-    <tableColumn id="9" name="Año"/>
-    <tableColumn id="10" name="Mes" totalsRowFunction="sum"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Cuenta"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Descripcion"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="SaldoAnterior"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Debito"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Credito"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="NuevoSaldo"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Empresa"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Pais"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Año"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Mes" totalsRowFunction="sum"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TablaCteYNoCte" displayName="TablaCteYNoCte" ref="A1:K2" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TablaCteYNoCte" displayName="TablaCteYNoCte" ref="A1:K2" totalsRowShown="0">
   <tableColumns count="11">
-    <tableColumn id="1" name="Cuenta"/>
-    <tableColumn id="2" name="Descripcion"/>
-    <tableColumn id="3" name="SaldoAnterior"/>
-    <tableColumn id="4" name="Debito"/>
-    <tableColumn id="5" name="Credito"/>
-    <tableColumn id="6" name="NuevoSaldo"/>
-    <tableColumn id="7" name="Empresa"/>
-    <tableColumn id="8" name="Pais"/>
-    <tableColumn id="9" name="Año"/>
-    <tableColumn id="10" name="Mes"/>
-    <tableColumn id="11" name="AcPa"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Cuenta"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Descripcion"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="SaldoAnterior"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Debito"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Credito"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="NuevoSaldo"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Empresa"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Pais"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Año"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Mes"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="AcPa"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TablaPYGDetallado" displayName="TablaPYGDetallado" ref="A1:K2" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="TablaPYGDetallado" displayName="TablaPYGDetallado" ref="A1:K2" totalsRowShown="0">
   <tableColumns count="11">
-    <tableColumn id="1" name="Cuenta"/>
-    <tableColumn id="2" name="Descripcion"/>
-    <tableColumn id="3" name="Tipo"/>
-    <tableColumn id="4" name="LineaNegocio"/>
-    <tableColumn id="5" name="NuevoSaldo"/>
-    <tableColumn id="6" name="Empresa"/>
-    <tableColumn id="7" name="Pais"/>
-    <tableColumn id="8" name="Año"/>
-    <tableColumn id="9" name="Mes"/>
-    <tableColumn id="10" name="Ajuste1"/>
-    <tableColumn id="11" name="Ajuste2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Cuenta"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Descripcion"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Tipo"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="LineaNegocio"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="NuevoSaldo"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Empresa"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Pais"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Año"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Mes"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Ajuste1"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Ajuste2"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TablaPYGDetalladoConAjuste" displayName="TablaPYGDetalladoConAjuste" ref="A1:K2" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="TablaPYGDetalladoConAjuste" displayName="TablaPYGDetalladoConAjuste" ref="A1:K2" totalsRowShown="0">
   <tableColumns count="11">
-    <tableColumn id="1" name="Cuenta"/>
-    <tableColumn id="2" name="Descripcion"/>
-    <tableColumn id="3" name="Tipo"/>
-    <tableColumn id="4" name="LineaNegocio"/>
-    <tableColumn id="5" name="NuevoSaldo"/>
-    <tableColumn id="6" name="Empresa"/>
-    <tableColumn id="7" name="Pais"/>
-    <tableColumn id="8" name="Año"/>
-    <tableColumn id="9" name="Mes"/>
-    <tableColumn id="10" name="Ajuste1"/>
-    <tableColumn id="11" name="Ajuste2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Cuenta"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Descripcion"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Tipo"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="LineaNegocio"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="NuevoSaldo"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Empresa"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Pais"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Año"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0300-000009000000}" name="Mes"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0300-00000A000000}" name="Ajuste1"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0300-00000B000000}" name="Ajuste2"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="TablaPresupuesto" displayName="TablaPresupuesto" ref="A1:G2" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="TablaPresupuesto" displayName="TablaPresupuesto" ref="A1:G2" totalsRowShown="0">
   <tableColumns count="7">
-    <tableColumn id="1" name="Cuenta"/>
-    <tableColumn id="2" name="Nombre"/>
-    <tableColumn id="3" name="Presupuesto"/>
-    <tableColumn id="4" name="Empresa"/>
-    <tableColumn id="5" name="Pais"/>
-    <tableColumn id="6" name="Año"/>
-    <tableColumn id="7" name="Mes"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Cuenta"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Nombre"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Presupuesto"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Empresa"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Pais"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Año"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="Mes"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="TablaPresupuestoDetallado" displayName="TablaPresupuestoDetallado" ref="A1:K2" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="TablaPresupuestoDetallado" displayName="TablaPresupuestoDetallado" ref="A1:K2" totalsRowShown="0">
   <tableColumns count="11">
-    <tableColumn id="1" name="Cuenta"/>
-    <tableColumn id="2" name="Descripcion"/>
-    <tableColumn id="3" name="Tipo"/>
-    <tableColumn id="4" name="LineaNegocio"/>
-    <tableColumn id="5" name="Saldo"/>
-    <tableColumn id="6" name="Empresa"/>
-    <tableColumn id="7" name="Pais"/>
-    <tableColumn id="8" name="Año"/>
-    <tableColumn id="9" name="Mes"/>
-    <tableColumn id="10" name="Ajuste1"/>
-    <tableColumn id="11" name="Ajuste2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Cuenta"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Descripcion"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Tipo"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="LineaNegocio"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Saldo"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Empresa"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Pais"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="Año"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0500-000009000000}" name="Mes"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0500-00000A000000}" name="Ajuste1"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0500-00000B000000}" name="Ajuste2"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="TablaPresupuestoDetallado18" displayName="TablaPresupuestoDetallado18" ref="A1:K2" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="TablaPresupuestoDetallado18" displayName="TablaPresupuestoDetallado18" ref="A1:K2" totalsRowShown="0">
   <tableColumns count="11">
-    <tableColumn id="1" name="Cuenta"/>
-    <tableColumn id="2" name="Descripcion"/>
-    <tableColumn id="3" name="Tipo"/>
-    <tableColumn id="4" name="LineaNegocio"/>
-    <tableColumn id="5" name="Saldo"/>
-    <tableColumn id="6" name="Empresa"/>
-    <tableColumn id="7" name="Pais"/>
-    <tableColumn id="8" name="Año"/>
-    <tableColumn id="9" name="Mes"/>
-    <tableColumn id="10" name="Ajuste1"/>
-    <tableColumn id="11" name="Ajuste2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Cuenta"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Descripcion"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Tipo"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="LineaNegocio"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="Saldo"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Empresa"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="Pais"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="Año"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="Mes"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="Ajuste1"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" name="Ajuste2"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="TablaPCH" displayName="TablaPCH" ref="A1:E36" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A1:E36"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="TablaPCH" displayName="TablaPCH" ref="A1:E36" totalsRowShown="0">
+  <autoFilter ref="A1:E36" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" name="Cuenta"/>
-    <tableColumn id="2" name="Nombre"/>
-    <tableColumn id="3" name="Valor"/>
-    <tableColumn id="4" name="Año"/>
-    <tableColumn id="5" name="Mes"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Cuenta"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Nombre"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Valor"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Año"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="Mes"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="TablaEjecPCH" displayName="TablaEjecPCH" ref="A1:E36" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A1:E36"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="TablaEjecPCH" displayName="TablaEjecPCH" ref="A1:E36" totalsRowShown="0">
+  <autoFilter ref="A1:E36" xr:uid="{00000000-0009-0000-0100-000009000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" name="Cuenta"/>
-    <tableColumn id="2" name="Nombre"/>
-    <tableColumn id="3" name="Valor"/>
-    <tableColumn id="4" name="Año"/>
-    <tableColumn id="5" name="Mes"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="Cuenta"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="Nombre"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="Valor"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Año"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="Mes"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1195,951 +1541,723 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF583AFF"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="25.28515625" defaultRowHeight="12.75"/>
   <cols>
-    <col width="13" customWidth="1" style="1" min="1" max="1"/>
-    <col width="15" customWidth="1" style="1" min="2" max="2"/>
-    <col width="17" customWidth="1" style="2" min="3" max="3"/>
-    <col width="13" customWidth="1" style="2" min="4" max="5"/>
-    <col width="14" customWidth="1" style="2" min="6" max="6"/>
-    <col width="13" customWidth="1" style="3" min="7" max="10"/>
-    <col width="25.28515625" customWidth="1" style="1" min="11" max="16384"/>
+    <col min="1" max="1" width="13" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17" style="2" customWidth="1"/>
+    <col min="4" max="5" width="13" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14" style="2" customWidth="1"/>
+    <col min="7" max="10" width="13" style="3" customWidth="1"/>
+    <col min="11" max="11" width="25.28515625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="25.28515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customFormat="1" customHeight="1" s="7">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Cuenta</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Descripcion</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>SaldoAnterior</t>
-        </is>
-      </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>Debito</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>Credito</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>NuevoSaldo</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>Empresa</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>Pais</t>
-        </is>
-      </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>Año</t>
-        </is>
-      </c>
-      <c r="J1" s="5" t="inlineStr">
-        <is>
-          <t>Mes</t>
-        </is>
+    <row r="1" spans="1:10" s="7" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="8" t="n"/>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="9" t="n"/>
-      <c r="F2" s="9" t="n"/>
-      <c r="G2" s="8" t="n"/>
-      <c r="H2" s="8" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
+    <row r="2" spans="1:10" ht="14.25" customHeight="1">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H501" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Lista_Pais</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="3"/>
+    <col min="1" max="3" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="28" t="inlineStr">
-        <is>
-          <t>Ajuste1</t>
-        </is>
-      </c>
-      <c r="B1" s="28" t="inlineStr">
-        <is>
-          <t>Ajuste2</t>
-        </is>
-      </c>
-      <c r="C1" s="28" t="inlineStr">
-        <is>
-          <t>AcPa</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Pais</t>
-        </is>
+    <row r="1" spans="1:4">
+      <c r="A1" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="29" t="inlineStr">
-        <is>
-          <t>Ebitda</t>
-        </is>
-      </c>
-      <c r="B2" s="29" t="inlineStr">
-        <is>
-          <t>GASTOS FIJOS</t>
-        </is>
-      </c>
-      <c r="C2" s="29" t="inlineStr">
-        <is>
-          <t>ACTIVO CORRIENTE</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Antigua y Barbuda</t>
-        </is>
+    <row r="2" spans="1:4">
+      <c r="A2" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="29" t="inlineStr">
-        <is>
-          <t>No Ebitda</t>
-        </is>
-      </c>
-      <c r="B3" s="29" t="inlineStr">
-        <is>
-          <t>VARIABLES</t>
-        </is>
-      </c>
-      <c r="C3" s="29" t="inlineStr">
-        <is>
-          <t>ACTIVO NO CORRIENTE</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
+    <row r="3" spans="1:4">
+      <c r="A3" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="29" t="inlineStr">
-        <is>
-          <t>OTROS GASTOS</t>
-        </is>
-      </c>
-      <c r="C4" s="29" t="inlineStr">
-        <is>
-          <t>PASIVO NO CORRIENTE</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Bahamas</t>
-        </is>
+    <row r="4" spans="1:4">
+      <c r="B4" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" t="s">
+        <v>49</v>
       </c>
     </row>
-    <row r="5">
-      <c r="C5" s="29" t="inlineStr">
-        <is>
-          <t>PASIVO CORRIENTE</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Barbados</t>
-        </is>
+    <row r="5" spans="1:4">
+      <c r="C5" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="6">
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Belice</t>
-        </is>
+    <row r="6" spans="1:4">
+      <c r="D6" t="s">
+        <v>52</v>
       </c>
     </row>
-    <row r="7">
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
+    <row r="7" spans="1:4">
+      <c r="D7" t="s">
+        <v>53</v>
       </c>
     </row>
-    <row r="8">
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
+    <row r="8" spans="1:4">
+      <c r="D8" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="9">
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Canadá</t>
-        </is>
+    <row r="9" spans="1:4">
+      <c r="D9" t="s">
+        <v>55</v>
       </c>
     </row>
-    <row r="10">
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Chile</t>
-        </is>
+    <row r="10" spans="1:4">
+      <c r="D10" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="11">
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
+    <row r="11" spans="1:4">
+      <c r="D11" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="12">
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Costa Rica</t>
-        </is>
+    <row r="12" spans="1:4">
+      <c r="D12" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="13">
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Cuba</t>
-        </is>
+    <row r="13" spans="1:4">
+      <c r="D13" t="s">
+        <v>59</v>
       </c>
     </row>
-    <row r="14">
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Dominica</t>
-        </is>
+    <row r="14" spans="1:4">
+      <c r="D14" t="s">
+        <v>60</v>
       </c>
     </row>
-    <row r="15">
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
+    <row r="15" spans="1:4">
+      <c r="D15" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="16">
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>El Salvador</t>
-        </is>
+    <row r="16" spans="1:4">
+      <c r="D16" t="s">
+        <v>62</v>
       </c>
     </row>
-    <row r="17">
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Estados Unidos</t>
-        </is>
+    <row r="17" spans="4:4">
+      <c r="D17" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="18">
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Granada</t>
-        </is>
+    <row r="18" spans="4:4">
+      <c r="D18" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="19">
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Guatemala</t>
-        </is>
+    <row r="19" spans="4:4">
+      <c r="D19" t="s">
+        <v>65</v>
       </c>
     </row>
-    <row r="20">
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
+    <row r="20" spans="4:4">
+      <c r="D20" t="s">
+        <v>66</v>
       </c>
     </row>
-    <row r="21">
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Haití</t>
-        </is>
+    <row r="21" spans="4:4">
+      <c r="D21" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="22">
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Honduras</t>
-        </is>
+    <row r="22" spans="4:4">
+      <c r="D22" t="s">
+        <v>68</v>
       </c>
     </row>
-    <row r="23">
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Jamaica</t>
-        </is>
+    <row r="23" spans="4:4">
+      <c r="D23" t="s">
+        <v>69</v>
       </c>
     </row>
-    <row r="24">
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>México</t>
-        </is>
+    <row r="24" spans="4:4">
+      <c r="D24" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="25">
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Nicaragua</t>
-        </is>
+    <row r="25" spans="4:4">
+      <c r="D25" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="26">
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Panamá</t>
-        </is>
+    <row r="26" spans="4:4">
+      <c r="D26" t="s">
+        <v>72</v>
       </c>
     </row>
-    <row r="27">
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
+    <row r="27" spans="4:4">
+      <c r="D27" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="28">
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Perú</t>
-        </is>
+    <row r="28" spans="4:4">
+      <c r="D28" t="s">
+        <v>74</v>
       </c>
     </row>
-    <row r="29">
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>República Dominicana</t>
-        </is>
+    <row r="29" spans="4:4">
+      <c r="D29" t="s">
+        <v>75</v>
       </c>
     </row>
-    <row r="30">
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>San Cristóbal y Nieves</t>
-        </is>
+    <row r="30" spans="4:4">
+      <c r="D30" t="s">
+        <v>76</v>
       </c>
     </row>
-    <row r="31">
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>San Vicente y las Granadinas</t>
-        </is>
+    <row r="31" spans="4:4">
+      <c r="D31" t="s">
+        <v>77</v>
       </c>
     </row>
-    <row r="32">
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Santa Lucía</t>
-        </is>
+    <row r="32" spans="4:4">
+      <c r="D32" t="s">
+        <v>78</v>
       </c>
     </row>
-    <row r="33">
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Suriname</t>
-        </is>
+    <row r="33" spans="4:4">
+      <c r="D33" t="s">
+        <v>82</v>
       </c>
     </row>
-    <row r="34">
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Trinidad y Tobago</t>
-        </is>
+    <row r="34" spans="4:4">
+      <c r="D34" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="35">
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
+    <row r="35" spans="4:4">
+      <c r="D35" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="36">
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
+    <row r="36" spans="4:4">
+      <c r="D36" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF583AFF"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="26.5703125" defaultRowHeight="12.75"/>
   <cols>
-    <col width="13" customWidth="1" style="1" min="1" max="1"/>
-    <col width="15" customWidth="1" style="1" min="2" max="2"/>
-    <col width="17" customWidth="1" style="11" min="3" max="3"/>
-    <col width="13" customWidth="1" style="11" min="4" max="5"/>
-    <col width="14" customWidth="1" style="11" min="6" max="6"/>
-    <col width="13" customWidth="1" style="1" min="7" max="11"/>
-    <col width="26.5703125" customWidth="1" style="12" min="12" max="16384"/>
+    <col min="1" max="1" width="13" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17" style="11" customWidth="1"/>
+    <col min="4" max="5" width="13" style="11" customWidth="1"/>
+    <col min="6" max="6" width="14" style="11" customWidth="1"/>
+    <col min="7" max="11" width="13" style="1" customWidth="1"/>
+    <col min="12" max="12" width="26.5703125" style="12" customWidth="1"/>
+    <col min="13" max="16384" width="26.5703125" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Cuenta</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Descripcion</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>SaldoAnterior</t>
-        </is>
-      </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>Debito</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>Credito</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>NuevoSaldo</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>Empresa</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>Pais</t>
-        </is>
-      </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>Año</t>
-        </is>
-      </c>
-      <c r="J1" s="5" t="inlineStr">
-        <is>
-          <t>Mes</t>
-        </is>
-      </c>
-      <c r="K1" s="5" t="inlineStr">
-        <is>
-          <t>AcPa</t>
-        </is>
+    <row r="1" spans="1:11" ht="19.5" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="8" t="n"/>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="9" t="n"/>
-      <c r="D2" s="9" t="n"/>
-      <c r="E2" s="9" t="n"/>
-      <c r="F2" s="9" t="n"/>
-      <c r="G2" s="8" t="n"/>
-      <c r="H2" s="8" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="8" t="n"/>
+    <row r="2" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="K2:K501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K501" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>Lista_AcPa</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="H2:H501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H501" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>Lista_Pais</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FF583AFF"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="12.75"/>
   <cols>
-    <col width="13" customWidth="1" style="12" min="1" max="1"/>
-    <col width="15" customWidth="1" style="12" min="2" max="2"/>
-    <col width="13" customWidth="1" style="12" min="3" max="3"/>
-    <col width="16" customWidth="1" style="12" min="4" max="4"/>
-    <col width="14" customWidth="1" style="13" min="5" max="5"/>
-    <col width="13" customWidth="1" style="12" min="6" max="7"/>
-    <col width="13" customWidth="1" style="14" min="8" max="8"/>
-    <col width="13" customWidth="1" style="12" min="9" max="11"/>
-    <col width="10.5703125" customWidth="1" style="12" min="12" max="16384"/>
+    <col min="1" max="1" width="13" style="12" customWidth="1"/>
+    <col min="2" max="2" width="15" style="12" customWidth="1"/>
+    <col min="3" max="3" width="13" style="12" customWidth="1"/>
+    <col min="4" max="4" width="16" style="12" customWidth="1"/>
+    <col min="5" max="5" width="14" style="13" customWidth="1"/>
+    <col min="6" max="7" width="13" style="12" customWidth="1"/>
+    <col min="8" max="8" width="13" style="14" customWidth="1"/>
+    <col min="9" max="11" width="13" style="12" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" style="12" customWidth="1"/>
+    <col min="13" max="16384" width="10.5703125" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customFormat="1" customHeight="1" s="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Cuenta</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Descripcion</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>LineaNegocio</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>NuevoSaldo</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>Empresa</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>Pais</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>Año</t>
-        </is>
-      </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>Mes</t>
-        </is>
-      </c>
-      <c r="J1" s="5" t="inlineStr">
-        <is>
-          <t>Ajuste1</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>Ajuste2</t>
-        </is>
+    <row r="1" spans="1:11" s="1" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customFormat="1" customHeight="1" s="1">
-      <c r="A2" s="8" t="n"/>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="9" t="n"/>
-      <c r="F2" s="8" t="n"/>
-      <c r="G2" s="8" t="n"/>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="8" t="n"/>
-      <c r="K2" s="8" t="n"/>
+    <row r="2" spans="1:11" s="1" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="J2:J501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J501" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>Lista_Ajuste1</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="K2:K501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K501" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>Lista_Ajuste2</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="G2:G501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G501" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>Lista_Pais</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor rgb="FF583AFF"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="12.75"/>
   <cols>
-    <col width="13" customWidth="1" style="12" min="1" max="1"/>
-    <col width="15" customWidth="1" style="12" min="2" max="2"/>
-    <col width="13" customWidth="1" style="12" min="3" max="3"/>
-    <col width="16" customWidth="1" style="12" min="4" max="4"/>
-    <col width="14" customWidth="1" style="13" min="5" max="5"/>
-    <col width="13" customWidth="1" style="12" min="6" max="7"/>
-    <col width="13" customWidth="1" style="14" min="8" max="8"/>
-    <col width="13" customWidth="1" style="12" min="9" max="11"/>
-    <col width="10.5703125" customWidth="1" style="12" min="12" max="16384"/>
+    <col min="1" max="1" width="13" style="12" customWidth="1"/>
+    <col min="2" max="2" width="15" style="12" customWidth="1"/>
+    <col min="3" max="3" width="13" style="12" customWidth="1"/>
+    <col min="4" max="4" width="16" style="12" customWidth="1"/>
+    <col min="5" max="5" width="14" style="13" customWidth="1"/>
+    <col min="6" max="7" width="13" style="12" customWidth="1"/>
+    <col min="8" max="8" width="13" style="14" customWidth="1"/>
+    <col min="9" max="11" width="13" style="12" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" style="12" customWidth="1"/>
+    <col min="13" max="16384" width="10.5703125" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customFormat="1" customHeight="1" s="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Cuenta</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Descripcion</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>LineaNegocio</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>NuevoSaldo</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>Empresa</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>Pais</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>Año</t>
-        </is>
-      </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>Mes</t>
-        </is>
-      </c>
-      <c r="J1" s="5" t="inlineStr">
-        <is>
-          <t>Ajuste1</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>Ajuste2</t>
-        </is>
+    <row r="1" spans="1:11" s="1" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="2" ht="14.25" customFormat="1" customHeight="1" s="1">
-      <c r="A2" s="15" t="n"/>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="9" t="n"/>
-      <c r="F2" s="8" t="n"/>
-      <c r="G2" s="8" t="n"/>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="8" t="n"/>
-      <c r="K2" s="8" t="n"/>
+    <row r="2" spans="1:11" s="1" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A2" s="15"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="J2:J501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J501" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>Lista_Ajuste1</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="K2:K501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K501" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>Lista_Ajuste2</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="G2:G501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G501" xr:uid="{00000000-0002-0000-0300-000002000000}">
       <formula1>Lista_Pais</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor rgb="FF583AFF"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75"/>
   <cols>
-    <col width="13" customWidth="1" style="12" min="1" max="2"/>
-    <col width="15" customWidth="1" style="12" min="3" max="3"/>
-    <col width="13" customWidth="1" style="12" min="4" max="7"/>
-    <col width="10.85546875" customWidth="1" style="12" min="8" max="16384"/>
+    <col min="1" max="2" width="13" style="12" customWidth="1"/>
+    <col min="3" max="3" width="15" style="12" customWidth="1"/>
+    <col min="4" max="7" width="13" style="12" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" style="12" customWidth="1"/>
+    <col min="9" max="16384" width="10.85546875" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Cuenta</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Nombre</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>Presupuesto</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>Empresa</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>Pais</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>Año</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>Mes</t>
-        </is>
+    <row r="1" spans="1:7" ht="19.5" customHeight="1">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="16" t="n"/>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="17" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
+    <row r="2" spans="1:7" ht="15.75" customHeight="1">
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E2:E501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E501" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>Lista_Pais</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor rgb="FF583AFF"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K8334"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="11.25"/>
   <cols>
-    <col width="13" customWidth="1" style="18" min="1" max="1"/>
-    <col width="15" customWidth="1" style="18" min="2" max="2"/>
-    <col width="13" customWidth="1" style="18" min="3" max="3"/>
-    <col width="16" customWidth="1" style="18" min="4" max="4"/>
-    <col width="13" customWidth="1" style="19" min="5" max="5"/>
-    <col width="13" customWidth="1" style="18" min="6" max="11"/>
-    <col width="10.5703125" customWidth="1" style="18" min="12" max="16384"/>
+    <col min="1" max="1" width="13" style="18" customWidth="1"/>
+    <col min="2" max="2" width="15" style="18" customWidth="1"/>
+    <col min="3" max="3" width="13" style="18" customWidth="1"/>
+    <col min="4" max="4" width="16" style="18" customWidth="1"/>
+    <col min="5" max="5" width="13" style="19" customWidth="1"/>
+    <col min="6" max="11" width="13" style="18" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" style="18" customWidth="1"/>
+    <col min="13" max="16384" width="10.5703125" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customFormat="1" customHeight="1" s="20">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Cuenta</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Descripcion</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>LineaNegocio</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>Saldo</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>Empresa</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>Pais</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>Año</t>
-        </is>
-      </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>Mes</t>
-        </is>
-      </c>
-      <c r="J1" s="5" t="inlineStr">
-        <is>
-          <t>Ajuste1</t>
-        </is>
-      </c>
-      <c r="K1" s="5" t="inlineStr">
-        <is>
-          <t>Ajuste2</t>
-        </is>
+    <row r="1" spans="1:11" s="20" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" s="8" t="n"/>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="9" t="n"/>
-      <c r="F2" s="8" t="n"/>
-      <c r="G2" s="8" t="n"/>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="8" t="n"/>
-      <c r="K2" s="8" t="n"/>
+    <row r="2" spans="1:11" ht="12.75" customHeight="1">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
     </row>
-    <row r="3" ht="12.75" customHeight="1"/>
-    <row r="4" ht="12.75" customHeight="1"/>
-    <row r="5" ht="12.75" customHeight="1"/>
-    <row r="6" ht="12.75" customHeight="1"/>
-    <row r="7" ht="12.75" customHeight="1"/>
-    <row r="8" ht="12.75" customHeight="1"/>
-    <row r="9" ht="12.75" customHeight="1"/>
-    <row r="10" ht="12.75" customHeight="1"/>
-    <row r="11" ht="12.75" customHeight="1"/>
-    <row r="12" ht="12.75" customHeight="1"/>
-    <row r="13" ht="12.75" customHeight="1"/>
-    <row r="14" ht="12.75" customHeight="1"/>
-    <row r="15" ht="12.75" customHeight="1"/>
-    <row r="16" ht="12.75" customHeight="1"/>
+    <row r="3" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="4" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="5" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="6" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="7" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="8" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="9" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="10" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="11" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="12" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="13" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="14" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="15" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="16" spans="1:11" ht="12.75" customHeight="1"/>
     <row r="17" ht="12.75" customHeight="1"/>
     <row r="18" ht="12.75" customHeight="1"/>
     <row r="19" ht="12.75" customHeight="1"/>
@@ -10460,131 +10578,108 @@
     <row r="8334" ht="14.25" customHeight="1"/>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="J2:J501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J501" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>Lista_Ajuste1</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="K2:K501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K501" xr:uid="{00000000-0002-0000-0500-000001000000}">
       <formula1>Lista_Ajuste2</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="G2:G501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G501" xr:uid="{00000000-0002-0000-0500-000002000000}">
       <formula1>Lista_Pais</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <tabColor rgb="FF583AFF"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K11597"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="11.25"/>
   <cols>
-    <col width="13" customWidth="1" style="21" min="1" max="1"/>
-    <col width="15" customWidth="1" style="21" min="2" max="2"/>
-    <col width="13" customWidth="1" style="21" min="3" max="3"/>
-    <col width="16" customWidth="1" style="21" min="4" max="4"/>
-    <col width="13" customWidth="1" style="22" min="5" max="5"/>
-    <col width="13" customWidth="1" style="21" min="6" max="10"/>
-    <col width="13" customWidth="1" style="18" min="11" max="11"/>
-    <col width="10.5703125" customWidth="1" style="21" min="12" max="16384"/>
+    <col min="1" max="1" width="13" style="21" customWidth="1"/>
+    <col min="2" max="2" width="15" style="21" customWidth="1"/>
+    <col min="3" max="3" width="13" style="21" customWidth="1"/>
+    <col min="4" max="4" width="16" style="21" customWidth="1"/>
+    <col min="5" max="5" width="13" style="22" customWidth="1"/>
+    <col min="6" max="10" width="13" style="21" customWidth="1"/>
+    <col min="11" max="11" width="13" style="18" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" style="21" customWidth="1"/>
+    <col min="13" max="16384" width="10.5703125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customFormat="1" customHeight="1" s="23">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Cuenta</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Descripcion</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>LineaNegocio</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>Saldo</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>Empresa</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>Pais</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>Año</t>
-        </is>
-      </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>Mes</t>
-        </is>
-      </c>
-      <c r="J1" s="5" t="inlineStr">
-        <is>
-          <t>Ajuste1</t>
-        </is>
-      </c>
-      <c r="K1" s="5" t="inlineStr">
-        <is>
-          <t>Ajuste2</t>
-        </is>
+    <row r="1" spans="1:11" s="23" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" s="8" t="n"/>
-      <c r="B2" s="8" t="n"/>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="9" t="n"/>
-      <c r="F2" s="8" t="n"/>
-      <c r="G2" s="8" t="n"/>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="8" t="n"/>
-      <c r="K2" s="8" t="n"/>
+    <row r="2" spans="1:11" ht="12.75" customHeight="1">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
     </row>
-    <row r="3" ht="12.75" customHeight="1"/>
-    <row r="4" ht="12.75" customHeight="1"/>
-    <row r="5" ht="12.75" customHeight="1"/>
-    <row r="6" ht="12.75" customHeight="1"/>
-    <row r="7" ht="12.75" customHeight="1"/>
-    <row r="8" ht="12.75" customHeight="1"/>
-    <row r="9" ht="12.75" customHeight="1"/>
-    <row r="10" ht="12.75" customHeight="1"/>
-    <row r="11" ht="12.75" customHeight="1"/>
-    <row r="12" ht="12.75" customHeight="1"/>
-    <row r="13" ht="12.75" customHeight="1"/>
-    <row r="14" ht="12.75" customHeight="1"/>
-    <row r="15" ht="12.75" customHeight="1"/>
-    <row r="16" ht="12.75" customHeight="1"/>
+    <row r="3" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="4" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="5" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="6" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="7" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="8" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="9" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="10" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="11" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="12" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="13" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="14" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="15" spans="1:11" ht="12.75" customHeight="1"/>
+    <row r="16" spans="1:11" ht="12.75" customHeight="1"/>
     <row r="17" ht="12.75" customHeight="1"/>
     <row r="18" ht="12.75" customHeight="1"/>
     <row r="19" ht="12.75" customHeight="1"/>
@@ -22168,1177 +22263,1013 @@
     <row r="11597" ht="15" customHeight="1"/>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="J2:J501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:J501" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>Lista_Ajuste1</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="K2:K501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2:K501" xr:uid="{00000000-0002-0000-0600-000001000000}">
       <formula1>Lista_Ajuste2</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="G2:G501" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G501" xr:uid="{00000000-0002-0000-0600-000002000000}">
       <formula1>Lista_Pais</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <tabColor rgb="FF583AFF"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="2"/>
-    <col width="13" customWidth="1" style="24" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="5"/>
+    <col min="1" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="13" style="24" customWidth="1"/>
+    <col min="4" max="5" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Cuenta</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Nombre</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>Año</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>Mes</t>
-        </is>
+    <row r="1" spans="1:5" ht="19.5" customHeight="1">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="25" t="n">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A2" s="25">
         <v>410</v>
       </c>
-      <c r="B2" s="25" t="inlineStr">
-        <is>
-          <t>Ingresos</t>
-        </is>
-      </c>
-      <c r="C2" s="26" t="n">
+      <c r="B2" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="26">
         <v>0</v>
       </c>
-      <c r="D2" s="27" t="n"/>
-      <c r="E2" s="27" t="n"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
     </row>
-    <row r="3">
-      <c r="A3" s="8" t="n">
+    <row r="3" spans="1:5">
+      <c r="A3" s="8">
         <v>51050</v>
       </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Gastos de personal</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="n">
+      <c r="B3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="9">
         <v>0</v>
       </c>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
     </row>
-    <row r="4">
-      <c r="A4" s="25" t="n">
+    <row r="4" spans="1:5">
+      <c r="A4" s="25">
         <v>51100</v>
       </c>
-      <c r="B4" s="25" t="inlineStr">
-        <is>
-          <t>Honorarios</t>
-        </is>
-      </c>
-      <c r="C4" s="26" t="n">
+      <c r="B4" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="26">
         <v>0</v>
       </c>
-      <c r="D4" s="27" t="n"/>
-      <c r="E4" s="27" t="n"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
     </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
+    <row r="5" spans="1:5">
+      <c r="A5" s="8">
         <v>51150</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Impuestos</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="n">
+      <c r="B5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="9">
         <v>0</v>
       </c>
-      <c r="D5" s="10" t="n"/>
-      <c r="E5" s="10" t="n"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
     </row>
-    <row r="6">
-      <c r="A6" s="25" t="n">
+    <row r="6" spans="1:5">
+      <c r="A6" s="25">
         <v>51200</v>
       </c>
-      <c r="B6" s="25" t="inlineStr">
-        <is>
-          <t>Arrendamientos</t>
-        </is>
-      </c>
-      <c r="C6" s="26" t="n">
+      <c r="B6" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="26">
         <v>0</v>
       </c>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="27" t="n"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
+    <row r="7" spans="1:5">
+      <c r="A7" s="8">
         <v>51250</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Contribuciones y afiliaciones</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="n">
+      <c r="B7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="9">
         <v>0</v>
       </c>
-      <c r="D7" s="10" t="n"/>
-      <c r="E7" s="10" t="n"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
     </row>
-    <row r="8">
-      <c r="A8" s="25" t="n">
+    <row r="8" spans="1:5">
+      <c r="A8" s="25">
         <v>51300</v>
       </c>
-      <c r="B8" s="25" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C8" s="26" t="n">
+      <c r="B8" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="26">
         <v>0</v>
       </c>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
+    <row r="9" spans="1:5">
+      <c r="A9" s="8">
         <v>51350</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Servicios</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="n">
+      <c r="B9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="9">
         <v>0</v>
       </c>
-      <c r="D9" s="10" t="n"/>
-      <c r="E9" s="10" t="n"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
     </row>
-    <row r="10">
-      <c r="A10" s="25" t="n">
+    <row r="10" spans="1:5">
+      <c r="A10" s="25">
         <v>51400</v>
       </c>
-      <c r="B10" s="25" t="inlineStr">
-        <is>
-          <t>Gastos legales</t>
-        </is>
-      </c>
-      <c r="C10" s="26" t="n">
+      <c r="B10" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="26">
         <v>0</v>
       </c>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="27" t="n"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
+    <row r="11" spans="1:5">
+      <c r="A11" s="8">
         <v>51450</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Mantenimiento y reparaciones</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="n">
+      <c r="B11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="9">
         <v>0</v>
       </c>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="10" t="n"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
     </row>
-    <row r="12">
-      <c r="A12" s="25" t="n">
+    <row r="12" spans="1:5">
+      <c r="A12" s="25">
         <v>51500</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
-        <is>
-          <t>Adecuación e instalación</t>
-        </is>
-      </c>
-      <c r="C12" s="26" t="n">
+      <c r="B12" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="26">
         <v>0</v>
       </c>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
     </row>
-    <row r="13">
-      <c r="A13" s="8" t="n">
+    <row r="13" spans="1:5">
+      <c r="A13" s="8">
         <v>51550</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Gastos de viaje</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="n">
+      <c r="B13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="9">
         <v>0</v>
       </c>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
     </row>
-    <row r="14">
-      <c r="A14" s="25" t="n">
+    <row r="14" spans="1:5">
+      <c r="A14" s="25">
         <v>51950</v>
       </c>
-      <c r="B14" s="25" t="inlineStr">
-        <is>
-          <t>Diversos</t>
-        </is>
-      </c>
-      <c r="C14" s="26" t="n">
+      <c r="B14" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="26">
         <v>0</v>
       </c>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
     </row>
-    <row r="15">
-      <c r="A15" s="8" t="n">
+    <row r="15" spans="1:5">
+      <c r="A15" s="8">
         <v>5199010</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Provisión Cartera</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="n">
+      <c r="B15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="9">
         <v>0</v>
       </c>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
     </row>
-    <row r="16">
-      <c r="A16" s="25" t="n">
+    <row r="16" spans="1:5">
+      <c r="A16" s="25">
         <v>5199020</v>
       </c>
-      <c r="B16" s="25" t="inlineStr">
-        <is>
-          <t>Provisión Inventario</t>
-        </is>
-      </c>
-      <c r="C16" s="26" t="n">
+      <c r="B16" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="26">
         <v>0</v>
       </c>
-      <c r="D16" s="27" t="n"/>
-      <c r="E16" s="27" t="n"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
     </row>
-    <row r="17">
-      <c r="A17" s="8" t="n">
+    <row r="17" spans="1:5">
+      <c r="A17" s="8">
         <v>52050</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Gastos de personal</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="n">
+      <c r="B17" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="9">
         <v>0</v>
       </c>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
     </row>
-    <row r="18">
-      <c r="A18" s="25" t="n">
+    <row r="18" spans="1:5">
+      <c r="A18" s="25">
         <v>52100</v>
       </c>
-      <c r="B18" s="25" t="inlineStr">
-        <is>
-          <t>Honorarios</t>
-        </is>
-      </c>
-      <c r="C18" s="26" t="n">
+      <c r="B18" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="26">
         <v>0</v>
       </c>
-      <c r="D18" s="27" t="n"/>
-      <c r="E18" s="27" t="n"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
     </row>
-    <row r="19">
-      <c r="A19" s="8" t="n">
+    <row r="19" spans="1:5">
+      <c r="A19" s="8">
         <v>52150</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Impuestos</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="n">
+      <c r="B19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="9">
         <v>0</v>
       </c>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
     </row>
-    <row r="20">
-      <c r="A20" s="25" t="n">
+    <row r="20" spans="1:5">
+      <c r="A20" s="25">
         <v>52200</v>
       </c>
-      <c r="B20" s="25" t="inlineStr">
-        <is>
-          <t>Arrendamientos</t>
-        </is>
-      </c>
-      <c r="C20" s="26" t="n">
+      <c r="B20" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="26">
         <v>0</v>
       </c>
-      <c r="D20" s="27" t="n"/>
-      <c r="E20" s="27" t="n"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
     </row>
-    <row r="21">
-      <c r="A21" s="8" t="n">
+    <row r="21" spans="1:5">
+      <c r="A21" s="8">
         <v>52250</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Contribuciones y afiliaciones</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="n">
+      <c r="B21" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="9">
         <v>0</v>
       </c>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
     </row>
-    <row r="22">
-      <c r="A22" s="25" t="n">
+    <row r="22" spans="1:5">
+      <c r="A22" s="25">
         <v>52300</v>
       </c>
-      <c r="B22" s="25" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C22" s="26" t="n">
+      <c r="B22" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="26">
         <v>0</v>
       </c>
-      <c r="D22" s="27" t="n"/>
-      <c r="E22" s="27" t="n"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
     </row>
-    <row r="23">
-      <c r="A23" s="8" t="n">
+    <row r="23" spans="1:5">
+      <c r="A23" s="8">
         <v>52350</v>
       </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Servicios</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="n">
+      <c r="B23" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="9">
         <v>0</v>
       </c>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="10" t="n"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
     </row>
-    <row r="24">
-      <c r="A24" s="25" t="n">
+    <row r="24" spans="1:5">
+      <c r="A24" s="25">
         <v>52400</v>
       </c>
-      <c r="B24" s="25" t="inlineStr">
-        <is>
-          <t>Gastos legales</t>
-        </is>
-      </c>
-      <c r="C24" s="26" t="n">
+      <c r="B24" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="26">
         <v>0</v>
       </c>
-      <c r="D24" s="27" t="n"/>
-      <c r="E24" s="27" t="n"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
     </row>
-    <row r="25">
-      <c r="A25" s="8" t="n">
+    <row r="25" spans="1:5">
+      <c r="A25" s="8">
         <v>52450</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Mantenimiento y reparaciones</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="n">
+      <c r="B25" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="9">
         <v>0</v>
       </c>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="10" t="n"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
     </row>
-    <row r="26">
-      <c r="A26" s="25" t="n">
+    <row r="26" spans="1:5">
+      <c r="A26" s="25">
         <v>52500</v>
       </c>
-      <c r="B26" s="25" t="inlineStr">
-        <is>
-          <t>Adecuación e instalación</t>
-        </is>
-      </c>
-      <c r="C26" s="26" t="n">
+      <c r="B26" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="26">
         <v>0</v>
       </c>
-      <c r="D26" s="27" t="n"/>
-      <c r="E26" s="27" t="n"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="n">
+    <row r="27" spans="1:5">
+      <c r="A27" s="8">
         <v>52550</v>
       </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>Gastos de viaje</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="n">
+      <c r="B27" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="9">
         <v>0</v>
       </c>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="10" t="n"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
     </row>
-    <row r="28">
-      <c r="A28" s="25" t="n">
+    <row r="28" spans="1:5">
+      <c r="A28" s="25">
         <v>52950</v>
       </c>
-      <c r="B28" s="25" t="inlineStr">
-        <is>
-          <t>Diversos</t>
-        </is>
-      </c>
-      <c r="C28" s="26" t="n">
+      <c r="B28" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="26">
         <v>0</v>
       </c>
-      <c r="D28" s="27" t="n"/>
-      <c r="E28" s="27" t="n"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
     </row>
-    <row r="29">
-      <c r="A29" s="8" t="n">
+    <row r="29" spans="1:5">
+      <c r="A29" s="8">
         <v>5299010</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Provisión Cartera</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="n">
+      <c r="B29" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="9">
         <v>0</v>
       </c>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="10" t="n"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
     </row>
-    <row r="30">
-      <c r="A30" s="25" t="n">
+    <row r="30" spans="1:5">
+      <c r="A30" s="25">
         <v>5299020</v>
       </c>
-      <c r="B30" s="25" t="inlineStr">
-        <is>
-          <t>Provisión Inventario</t>
-        </is>
-      </c>
-      <c r="C30" s="26" t="n">
+      <c r="B30" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="26">
         <v>0</v>
       </c>
-      <c r="D30" s="27" t="n"/>
-      <c r="E30" s="27" t="n"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
     </row>
-    <row r="31">
-      <c r="A31" s="8" t="n">
+    <row r="31" spans="1:5">
+      <c r="A31" s="8">
         <v>42050</v>
       </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Otras ventas</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="n">
+      <c r="B31" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="9">
         <v>0</v>
       </c>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="10" t="n"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
     </row>
-    <row r="32">
-      <c r="A32" s="25" t="n">
+    <row r="32" spans="1:5">
+      <c r="A32" s="25">
         <v>42500</v>
       </c>
-      <c r="B32" s="25" t="inlineStr">
-        <is>
-          <t>Recuperaciones</t>
-        </is>
-      </c>
-      <c r="C32" s="26" t="n">
+      <c r="B32" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="26">
         <v>0</v>
       </c>
-      <c r="D32" s="27" t="n"/>
-      <c r="E32" s="27" t="n"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
     </row>
-    <row r="33">
-      <c r="A33" s="8" t="n">
+    <row r="33" spans="1:5">
+      <c r="A33" s="8">
         <v>42150</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Diversos</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="n">
+      <c r="B33" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="9">
         <v>0</v>
       </c>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="n"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
     </row>
-    <row r="34">
-      <c r="A34" s="25" t="n">
+    <row r="34" spans="1:5">
+      <c r="A34" s="25">
         <v>53100</v>
       </c>
-      <c r="B34" s="25" t="inlineStr">
-        <is>
-          <t>Pérdida en venta y retiro de bienes</t>
-        </is>
-      </c>
-      <c r="C34" s="26" t="n">
+      <c r="B34" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" s="26">
         <v>0</v>
       </c>
-      <c r="D34" s="27" t="n"/>
-      <c r="E34" s="27" t="n"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
     </row>
-    <row r="35">
-      <c r="A35" s="8" t="n">
+    <row r="35" spans="1:5">
+      <c r="A35" s="8">
         <v>53150</v>
       </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Gastos extraordinarios</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="n">
+      <c r="B35" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" s="9">
         <v>0</v>
       </c>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
     </row>
-    <row r="36">
-      <c r="A36" s="25" t="n">
+    <row r="36" spans="1:5">
+      <c r="A36" s="25">
         <v>53130</v>
       </c>
-      <c r="B36" s="25" t="inlineStr">
-        <is>
-          <t>Gastos diversos</t>
-        </is>
-      </c>
-      <c r="C36" s="26" t="n">
+      <c r="B36" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="26">
         <v>0</v>
       </c>
-      <c r="D36" s="27" t="n"/>
-      <c r="E36" s="27" t="n"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor rgb="FF583AFF"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="2"/>
-    <col width="13" customWidth="1" style="24" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="5"/>
+    <col min="1" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="13" style="24" customWidth="1"/>
+    <col min="4" max="5" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Cuenta</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Nombre</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>Año</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>Mes</t>
-        </is>
+    <row r="1" spans="1:5" ht="19.5" customHeight="1">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="25" t="n">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A2" s="25">
         <v>410</v>
       </c>
-      <c r="B2" s="25" t="inlineStr">
-        <is>
-          <t>Ingresos</t>
-        </is>
-      </c>
-      <c r="C2" s="26" t="n">
+      <c r="B2" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="26">
         <v>0</v>
       </c>
-      <c r="D2" s="27" t="n"/>
-      <c r="E2" s="27" t="n"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
     </row>
-    <row r="3">
-      <c r="A3" s="8" t="n">
+    <row r="3" spans="1:5">
+      <c r="A3" s="8">
         <v>51050</v>
       </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Gastos de personal</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="n">
+      <c r="B3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="9">
         <v>0</v>
       </c>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
     </row>
-    <row r="4">
-      <c r="A4" s="25" t="n">
+    <row r="4" spans="1:5">
+      <c r="A4" s="25">
         <v>51100</v>
       </c>
-      <c r="B4" s="25" t="inlineStr">
-        <is>
-          <t>Honorarios</t>
-        </is>
-      </c>
-      <c r="C4" s="26" t="n">
+      <c r="B4" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="26">
         <v>0</v>
       </c>
-      <c r="D4" s="27" t="n"/>
-      <c r="E4" s="27" t="n"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
     </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
+    <row r="5" spans="1:5">
+      <c r="A5" s="8">
         <v>51150</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Impuestos</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="n">
+      <c r="B5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="9">
         <v>0</v>
       </c>
-      <c r="D5" s="10" t="n"/>
-      <c r="E5" s="10" t="n"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
     </row>
-    <row r="6">
-      <c r="A6" s="25" t="n">
+    <row r="6" spans="1:5">
+      <c r="A6" s="25">
         <v>51200</v>
       </c>
-      <c r="B6" s="25" t="inlineStr">
-        <is>
-          <t>Arrendamientos</t>
-        </is>
-      </c>
-      <c r="C6" s="26" t="n">
+      <c r="B6" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="26">
         <v>0</v>
       </c>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="27" t="n"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="n">
+    <row r="7" spans="1:5">
+      <c r="A7" s="8">
         <v>51250</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Contribuciones y afiliaciones</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="n">
+      <c r="B7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="9">
         <v>0</v>
       </c>
-      <c r="D7" s="10" t="n"/>
-      <c r="E7" s="10" t="n"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
     </row>
-    <row r="8">
-      <c r="A8" s="25" t="n">
+    <row r="8" spans="1:5">
+      <c r="A8" s="25">
         <v>51300</v>
       </c>
-      <c r="B8" s="25" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C8" s="26" t="n">
+      <c r="B8" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="26">
         <v>0</v>
       </c>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="n">
+    <row r="9" spans="1:5">
+      <c r="A9" s="8">
         <v>51350</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Servicios</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="n">
+      <c r="B9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="9">
         <v>0</v>
       </c>
-      <c r="D9" s="10" t="n"/>
-      <c r="E9" s="10" t="n"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
     </row>
-    <row r="10">
-      <c r="A10" s="25" t="n">
+    <row r="10" spans="1:5">
+      <c r="A10" s="25">
         <v>51400</v>
       </c>
-      <c r="B10" s="25" t="inlineStr">
-        <is>
-          <t>Gastos legales</t>
-        </is>
-      </c>
-      <c r="C10" s="26" t="n">
+      <c r="B10" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="26">
         <v>0</v>
       </c>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="27" t="n"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="n">
+    <row r="11" spans="1:5">
+      <c r="A11" s="8">
         <v>51450</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Mantenimiento y reparaciones</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="n">
+      <c r="B11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="9">
         <v>0</v>
       </c>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="10" t="n"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
     </row>
-    <row r="12">
-      <c r="A12" s="25" t="n">
+    <row r="12" spans="1:5">
+      <c r="A12" s="25">
         <v>51500</v>
       </c>
-      <c r="B12" s="25" t="inlineStr">
-        <is>
-          <t>Adecuación e instalación</t>
-        </is>
-      </c>
-      <c r="C12" s="26" t="n">
+      <c r="B12" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="26">
         <v>0</v>
       </c>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
     </row>
-    <row r="13">
-      <c r="A13" s="8" t="n">
+    <row r="13" spans="1:5">
+      <c r="A13" s="8">
         <v>51550</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Gastos de viaje</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="n">
+      <c r="B13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="9">
         <v>0</v>
       </c>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
     </row>
-    <row r="14">
-      <c r="A14" s="25" t="n">
+    <row r="14" spans="1:5">
+      <c r="A14" s="25">
         <v>51950</v>
       </c>
-      <c r="B14" s="25" t="inlineStr">
-        <is>
-          <t>Diversos</t>
-        </is>
-      </c>
-      <c r="C14" s="26" t="n">
+      <c r="B14" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="26">
         <v>0</v>
       </c>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
     </row>
-    <row r="15">
-      <c r="A15" s="8" t="n">
+    <row r="15" spans="1:5">
+      <c r="A15" s="8">
         <v>5199010</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Provisión Cartera</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="n">
+      <c r="B15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="9">
         <v>0</v>
       </c>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="10" t="n"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
     </row>
-    <row r="16">
-      <c r="A16" s="25" t="n">
+    <row r="16" spans="1:5">
+      <c r="A16" s="25">
         <v>5199020</v>
       </c>
-      <c r="B16" s="25" t="inlineStr">
-        <is>
-          <t>Provisión Inventario</t>
-        </is>
-      </c>
-      <c r="C16" s="26" t="n">
+      <c r="B16" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="26">
         <v>0</v>
       </c>
-      <c r="D16" s="27" t="n"/>
-      <c r="E16" s="27" t="n"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
     </row>
-    <row r="17">
-      <c r="A17" s="8" t="n">
+    <row r="17" spans="1:5">
+      <c r="A17" s="8">
         <v>52050</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>Gastos de personal</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="n">
+      <c r="B17" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="9">
         <v>0</v>
       </c>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="10" t="n"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
     </row>
-    <row r="18">
-      <c r="A18" s="25" t="n">
+    <row r="18" spans="1:5">
+      <c r="A18" s="25">
         <v>52100</v>
       </c>
-      <c r="B18" s="25" t="inlineStr">
-        <is>
-          <t>Honorarios</t>
-        </is>
-      </c>
-      <c r="C18" s="26" t="n">
+      <c r="B18" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="26">
         <v>0</v>
       </c>
-      <c r="D18" s="27" t="n"/>
-      <c r="E18" s="27" t="n"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
     </row>
-    <row r="19">
-      <c r="A19" s="8" t="n">
+    <row r="19" spans="1:5">
+      <c r="A19" s="8">
         <v>52150</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>Impuestos</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="n">
+      <c r="B19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="9">
         <v>0</v>
       </c>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
     </row>
-    <row r="20">
-      <c r="A20" s="25" t="n">
+    <row r="20" spans="1:5">
+      <c r="A20" s="25">
         <v>52200</v>
       </c>
-      <c r="B20" s="25" t="inlineStr">
-        <is>
-          <t>Arrendamientos</t>
-        </is>
-      </c>
-      <c r="C20" s="26" t="n">
+      <c r="B20" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="26">
         <v>0</v>
       </c>
-      <c r="D20" s="27" t="n"/>
-      <c r="E20" s="27" t="n"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
     </row>
-    <row r="21">
-      <c r="A21" s="8" t="n">
+    <row r="21" spans="1:5">
+      <c r="A21" s="8">
         <v>52250</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Contribuciones y afiliaciones</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="n">
+      <c r="B21" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="9">
         <v>0</v>
       </c>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
     </row>
-    <row r="22">
-      <c r="A22" s="25" t="n">
+    <row r="22" spans="1:5">
+      <c r="A22" s="25">
         <v>52300</v>
       </c>
-      <c r="B22" s="25" t="inlineStr">
-        <is>
-          <t>Seguros</t>
-        </is>
-      </c>
-      <c r="C22" s="26" t="n">
+      <c r="B22" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="26">
         <v>0</v>
       </c>
-      <c r="D22" s="27" t="n"/>
-      <c r="E22" s="27" t="n"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
     </row>
-    <row r="23">
-      <c r="A23" s="8" t="n">
+    <row r="23" spans="1:5">
+      <c r="A23" s="8">
         <v>52350</v>
       </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Servicios</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="n">
+      <c r="B23" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="9">
         <v>0</v>
       </c>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="10" t="n"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
     </row>
-    <row r="24">
-      <c r="A24" s="25" t="n">
+    <row r="24" spans="1:5">
+      <c r="A24" s="25">
         <v>52400</v>
       </c>
-      <c r="B24" s="25" t="inlineStr">
-        <is>
-          <t>Gastos legales</t>
-        </is>
-      </c>
-      <c r="C24" s="26" t="n">
+      <c r="B24" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="26">
         <v>0</v>
       </c>
-      <c r="D24" s="27" t="n"/>
-      <c r="E24" s="27" t="n"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
     </row>
-    <row r="25">
-      <c r="A25" s="8" t="n">
+    <row r="25" spans="1:5">
+      <c r="A25" s="8">
         <v>52450</v>
       </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Mantenimiento y reparaciones</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="n">
+      <c r="B25" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="9">
         <v>0</v>
       </c>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="10" t="n"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
     </row>
-    <row r="26">
-      <c r="A26" s="25" t="n">
+    <row r="26" spans="1:5">
+      <c r="A26" s="25">
         <v>52500</v>
       </c>
-      <c r="B26" s="25" t="inlineStr">
-        <is>
-          <t>Adecuación e instalación</t>
-        </is>
-      </c>
-      <c r="C26" s="26" t="n">
+      <c r="B26" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="26">
         <v>0</v>
       </c>
-      <c r="D26" s="27" t="n"/>
-      <c r="E26" s="27" t="n"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="n">
+    <row r="27" spans="1:5">
+      <c r="A27" s="8">
         <v>52550</v>
       </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>Gastos de viaje</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="n">
+      <c r="B27" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="9">
         <v>0</v>
       </c>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="10" t="n"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
     </row>
-    <row r="28">
-      <c r="A28" s="25" t="n">
+    <row r="28" spans="1:5">
+      <c r="A28" s="25">
         <v>52950</v>
       </c>
-      <c r="B28" s="25" t="inlineStr">
-        <is>
-          <t>Diversos</t>
-        </is>
-      </c>
-      <c r="C28" s="26" t="n">
+      <c r="B28" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="26">
         <v>0</v>
       </c>
-      <c r="D28" s="27" t="n"/>
-      <c r="E28" s="27" t="n"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
     </row>
-    <row r="29">
-      <c r="A29" s="8" t="n">
+    <row r="29" spans="1:5">
+      <c r="A29" s="8">
         <v>5299010</v>
       </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Provisión Cartera</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="n">
+      <c r="B29" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="9">
         <v>0</v>
       </c>
-      <c r="D29" s="10" t="n"/>
-      <c r="E29" s="10" t="n"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
     </row>
-    <row r="30">
-      <c r="A30" s="25" t="n">
+    <row r="30" spans="1:5">
+      <c r="A30" s="25">
         <v>5299020</v>
       </c>
-      <c r="B30" s="25" t="inlineStr">
-        <is>
-          <t>Provisión Inventario</t>
-        </is>
-      </c>
-      <c r="C30" s="26" t="n">
+      <c r="B30" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" s="26">
         <v>0</v>
       </c>
-      <c r="D30" s="27" t="n"/>
-      <c r="E30" s="27" t="n"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
     </row>
-    <row r="31">
-      <c r="A31" s="8" t="n">
+    <row r="31" spans="1:5">
+      <c r="A31" s="8">
         <v>42050</v>
       </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Otras ventas</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="n">
+      <c r="B31" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="9">
         <v>0</v>
       </c>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="10" t="n"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
     </row>
-    <row r="32">
-      <c r="A32" s="25" t="n">
+    <row r="32" spans="1:5">
+      <c r="A32" s="25">
         <v>42500</v>
       </c>
-      <c r="B32" s="25" t="inlineStr">
-        <is>
-          <t>Recuperaciones</t>
-        </is>
-      </c>
-      <c r="C32" s="26" t="n">
+      <c r="B32" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="26">
         <v>0</v>
       </c>
-      <c r="D32" s="27" t="n"/>
-      <c r="E32" s="27" t="n"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
     </row>
-    <row r="33">
-      <c r="A33" s="8" t="n">
+    <row r="33" spans="1:5">
+      <c r="A33" s="8">
         <v>42150</v>
       </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Diversos</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="n">
+      <c r="B33" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="9">
         <v>0</v>
       </c>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="n"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
     </row>
-    <row r="34">
-      <c r="A34" s="25" t="n">
+    <row r="34" spans="1:5">
+      <c r="A34" s="25">
         <v>53100</v>
       </c>
-      <c r="B34" s="25" t="inlineStr">
-        <is>
-          <t>Pérdida en venta y retiro de bienes</t>
-        </is>
-      </c>
-      <c r="C34" s="26" t="n">
+      <c r="B34" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" s="26">
         <v>0</v>
       </c>
-      <c r="D34" s="27" t="n"/>
-      <c r="E34" s="27" t="n"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
     </row>
-    <row r="35">
-      <c r="A35" s="8" t="n">
+    <row r="35" spans="1:5">
+      <c r="A35" s="8">
         <v>53150</v>
       </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>Gastos extraordinarios</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="n">
+      <c r="B35" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" s="9">
         <v>0</v>
       </c>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
     </row>
-    <row r="36">
-      <c r="A36" s="25" t="n">
+    <row r="36" spans="1:5">
+      <c r="A36" s="25">
         <v>53130</v>
       </c>
-      <c r="B36" s="25" t="inlineStr">
-        <is>
-          <t>Gastos diversos</t>
-        </is>
-      </c>
-      <c r="C36" s="26" t="n">
+      <c r="B36" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="26">
         <v>0</v>
       </c>
-      <c r="D36" s="27" t="n"/>
-      <c r="E36" s="27" t="n"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Assets/Plantillas/PlantillaBUFINS.xlsx
+++ b/Assets/Plantillas/PlantillaBUFINS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\omara_\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://coopmind-my.sharepoint.com/personal/power_coopmind_onmicrosoft_com/Documents/00. Modelo financiero 2025 sin macros/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3FC022C-8F91-419A-831B-23016672EBFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="8_{36350B45-7EBC-499D-9504-7EB5FF214A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F063AF52-30B9-425D-A742-B9B5C8F7AEB9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Z_BalancePrueba" sheetId="1" r:id="rId1"/>
@@ -30,31 +30,35 @@
     <definedName name="Lista_Ajuste2">Datos!$B$2:$B$4</definedName>
     <definedName name="Lista_Pais">Datos!$D$2:$D$36</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Unknown Author</author>
+    <author>tc={DEABBE3B-3B69-41F6-92E6-ABC527FA7BB2}</author>
   </authors>
   <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{DEABBE3B-3B69-41F6-92E6-ABC527FA7BB2}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t>[Comentario encadenado]
+        <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
-    El  Z_BalancePrueba debe estar a 1, 2, 4 y 6 dígitos del PUC</t>
-        </r>
+    El  Z_BalancePrueba debe estar a 1, 2, 4 y 6 dígitos del PUC. Incluir el movimiento completo de las cuentas</t>
       </text>
     </comment>
   </commentList>
@@ -64,24 +68,15 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Unknown Author</author>
+    <author>tc={DBE417B5-B83D-44CA-B614-E53B59EA954F}</author>
   </authors>
   <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{DBE417B5-B83D-44CA-B614-E53B59EA954F}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">[Comentario encadenado]
+        <t xml:space="preserve">[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Las cuentas Z_CteYnoCte deben estar a 4 dígitos del PUC. Solo debe incluir las cuentas de balance que tienen porción corriente y no corriente e incluir el movimiento completo de las cuentas. </t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -91,24 +86,17 @@
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Unknown Author</author>
+    <author>tc={8A09B200-0C98-49B4-B440-C9E049F8B8B3}</author>
   </authors>
   <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{8A09B200-0C98-49B4-B440-C9E049F8B8B3}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t>[Comentario encadenado]
+        <t xml:space="preserve">[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
-    Las cuentas Z_PYGDetallado deben estar a 6 dígitos del PUC</t>
-        </r>
+    Las cuentas Z_PYGDetallado deben estar a 6 dígitos del PUC y el signo de las cuentas debe conservar el mismo del balance de prueba. El ajuste 1 está relacionado con los ajustes del Ebitda que deban hacerse.  
+Tenga en cuenta que el nuevo saldo debe ser el valor del mes de los ingresos, los costos y los gastos.
+</t>
       </text>
     </comment>
   </commentList>
@@ -118,24 +106,17 @@
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Unknown Author</author>
+    <author>tc={3C2852B4-714B-46DC-8067-B69E12F6988E}</author>
   </authors>
   <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{3C2852B4-714B-46DC-8067-B69E12F6988E}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t>[Comentario encadenado]
+        <t xml:space="preserve">[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
-    Las cuentas Z_PYGDetalladoConAjuste deben estar a 6 dígitos del PUC</t>
-        </r>
+    Las cuentas Z_PYGDetallado deben estar a 6 dígitos del PUC y el signo de las cuentas debe conservar el mismo del balance de prueba. El ajuste 1 está relacionado con los ajustes del Ebitda que deban hacerse.  
+Tenga en cuenta que el nuevo saldo debe ser el valor del mes de los ingresos, los costos y los gastos.
+</t>
       </text>
     </comment>
   </commentList>
@@ -145,24 +126,16 @@
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Unknown Author</author>
+    <author>tc={76C75068-60C9-48D9-932D-7F8A7C475D72}</author>
   </authors>
   <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{76C75068-60C9-48D9-932D-7F8A7C475D72}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t>[Comentario encadenado]
+        <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
-    Las cuentas Z_PresupuestoBalance deben estar a 1, 2, 4 y 6 dígitos del PUC</t>
-        </r>
+    Las cuentas Z_PresupuestoBalance deben estar a 1, 2, 4 y 6 dígitos del PUC.
+Si la empresa no tiene presupuesto en Bufins se elabora con los supuestos suministrados por el cliente.</t>
       </text>
     </comment>
   </commentList>
@@ -172,24 +145,17 @@
 <file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Unknown Author</author>
+    <author>tc={DDF1AFFB-FEAB-425E-9DA7-40A83EF3F3BA}</author>
   </authors>
   <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000001000000}">
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{DDF1AFFB-FEAB-425E-9DA7-40A83EF3F3BA}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t>[Comentario encadenado]
+        <t xml:space="preserve">[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
-    Las cuentas Z_PptoPYGDetallado deben estar a 6 dígitos del PUC</t>
-        </r>
+    Las cuentas Z_PYGDetallado deben estar a 6 dígitos del PUC y la cuenta 4 debe ser negativa.
+Tenga en cuenta que el nuevo saldo debe ser el valor del mes de los ingresos, los costos y los gastos.
+</t>
       </text>
     </comment>
   </commentList>
@@ -199,24 +165,18 @@
 <file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Unknown Author</author>
+    <author>tc={3BAE724E-6502-4301-B51C-51213B67D22C}</author>
   </authors>
   <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{3BAE724E-6502-4301-B51C-51213B67D22C}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t>[Comentario encadenado]
+        <t xml:space="preserve">[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
-    Las cuentas Z_PptoPYGDetalladoConAjuste deben estar a 6 dígitos del PUC</t>
-        </r>
+    Las cuentas Z_PYGDetallado deben estar a 6 dígitos del PUC y la cuenta 4 debe ser negativa.
+El ajuste 1 está relacionado con los ajustes del Ebitda que deban hacerse.  
+Tenga en cuenta que el nuevo saldo debe ser el valor del mes de los ingresos, los costos y los gastos.
+</t>
       </text>
     </comment>
   </commentList>
@@ -226,24 +186,15 @@
 <file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Unknown Author</author>
+    <author>tc={AF05B4E4-3C4F-457D-8348-8261667E1A2D}</author>
   </authors>
   <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000001000000}">
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{AF05B4E4-3C4F-457D-8348-8261667E1A2D}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t>[Comentario encadenado]
+        <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Las cuentas Z_PCH son las que se detallan en esta plantilla</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -253,24 +204,15 @@
 <file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Unknown Author</author>
+    <author>tc={E0AAEAF1-2CE1-4C73-879E-A775F3930A83}</author>
   </authors>
   <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000001000000}">
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{E0AAEAF1-2CE1-4C73-879E-A775F3930A83}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <charset val="1"/>
-          </rPr>
-          <t>[Comentario encadenado]
+        <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Las cuentas Z_PCH son las que se detallan en esta plantilla</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -642,7 +584,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -665,6 +607,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF2EFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -893,7 +847,7 @@
     <xf numFmtId="3" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -920,9 +874,6 @@
     <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -942,6 +893,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="184">
     <cellStyle name="Comma 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -1129,7 +1084,308 @@
     <cellStyle name="Normal 9" xfId="182" xr:uid="{00000000-0005-0000-0000-0000B6000000}"/>
     <cellStyle name="Porcentaje 2" xfId="183" xr:uid="{00000000-0005-0000-0000-0000B7000000}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Cyntho"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF583AFF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF583AFF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF583AFF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF583AFF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Cyntho"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF583AFF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF583AFF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF583AFF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF583AFF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FF583AFF"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Cyntho"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF583AFF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF583AFF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF583AFF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF583AFF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Cyntho"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF583AFF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF583AFF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF583AFF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF583AFF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Cyntho"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF583AFF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF583AFF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF583AFF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF583AFF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Cyntho"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF583AFF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF583AFF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF583AFF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF583AFF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Cyntho"/>
+        <charset val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FF583AFF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF583AFF"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF583AFF"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF583AFF"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -1210,10 +1466,16 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Marta Elena Hoyos Naranjo" id="{4F71464B-9EDC-4362-9909-93CA2C7CF031}" userId="S::power@coopmind.onmicrosoft.com::7c2ac774-9325-41fd-b4c6-0b9342806904" providerId="AD"/>
+</personList>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaBalance" displayName="TablaBalance" ref="A1:J2" totalsRowShown="0">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Cuenta"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Cuenta" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Descripcion"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="SaldoAnterior"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Debito"/>
@@ -1231,7 +1493,7 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TablaCteYNoCte" displayName="TablaCteYNoCte" ref="A1:K2" totalsRowShown="0">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Cuenta"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Cuenta" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Descripcion"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="SaldoAnterior"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Debito"/>
@@ -1250,7 +1512,7 @@
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="TablaPYGDetallado" displayName="TablaPYGDetallado" ref="A1:K2" totalsRowShown="0">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Cuenta"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Cuenta" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Descripcion"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Tipo"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="LineaNegocio"/>
@@ -1269,7 +1531,7 @@
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="TablaPYGDetalladoConAjuste" displayName="TablaPYGDetalladoConAjuste" ref="A1:K2" totalsRowShown="0">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Cuenta"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Cuenta" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Descripcion"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Tipo"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="LineaNegocio"/>
@@ -1288,8 +1550,8 @@
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="TablaPresupuesto" displayName="TablaPresupuesto" ref="A1:G2" totalsRowShown="0">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Cuenta"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Nombre"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Cuenta" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Nombre" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Presupuesto"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Empresa"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Pais"/>
@@ -1303,7 +1565,7 @@
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="TablaPresupuestoDetallado" displayName="TablaPresupuestoDetallado" ref="A1:K2" totalsRowShown="0">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Cuenta"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Cuenta" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Descripcion"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Tipo"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="LineaNegocio"/>
@@ -1322,7 +1584,7 @@
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="TablaPresupuestoDetallado18" displayName="TablaPresupuestoDetallado18" ref="A1:K2" totalsRowShown="0">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Cuenta"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Cuenta" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Descripcion"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Tipo"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="LineaNegocio"/>
@@ -1540,6 +1802,88 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A2" dT="2024-05-04T16:42:21.57" personId="{4F71464B-9EDC-4362-9909-93CA2C7CF031}" id="{DEABBE3B-3B69-41F6-92E6-ABC527FA7BB2}">
+    <text>El  Z_BalancePrueba debe estar a 1, 2, 4 y 6 dígitos del PUC. Incluir el movimiento completo de las cuentas</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A2" dT="2024-05-04T16:40:55.66" personId="{4F71464B-9EDC-4362-9909-93CA2C7CF031}" id="{DBE417B5-B83D-44CA-B614-E53B59EA954F}">
+    <text xml:space="preserve">Las cuentas Z_CteYnoCte deben estar a 4 dígitos del PUC. Solo debe incluir las cuentas de balance que tienen porción corriente y no corriente e incluir el movimiento completo de las cuentas. </text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A2" dT="2024-05-04T16:41:46.15" personId="{4F71464B-9EDC-4362-9909-93CA2C7CF031}" id="{8A09B200-0C98-49B4-B440-C9E049F8B8B3}">
+    <text xml:space="preserve">Las cuentas Z_PYGDetallado deben estar a 6 dígitos del PUC y el signo de las cuentas debe conservar el mismo del balance de prueba. El ajuste 1 está relacionado con los ajustes del Ebitda que deban hacerse.  
+Tenga en cuenta que el nuevo saldo debe ser el valor del mes de los ingresos, los costos y los gastos.
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment4.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A2" dT="2024-05-04T16:41:46.15" personId="{4F71464B-9EDC-4362-9909-93CA2C7CF031}" id="{3C2852B4-714B-46DC-8067-B69E12F6988E}">
+    <text xml:space="preserve">Las cuentas Z_PYGDetallado deben estar a 6 dígitos del PUC y el signo de las cuentas debe conservar el mismo del balance de prueba. El ajuste 1 está relacionado con los ajustes del Ebitda que deban hacerse.  
+Tenga en cuenta que el nuevo saldo debe ser el valor del mes de los ingresos, los costos y los gastos.
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment5.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A2" dT="2024-05-04T16:41:46.15" personId="{4F71464B-9EDC-4362-9909-93CA2C7CF031}" id="{76C75068-60C9-48D9-932D-7F8A7C475D72}">
+    <text>Las cuentas Z_PresupuestoBalance deben estar a 1, 2, 4 y 6 dígitos del PUC.
+Si la empresa no tiene presupuesto en Bufins se elabora con los supuestos suministrados por el cliente.</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment6.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A2" dT="2024-05-04T16:41:46.15" personId="{4F71464B-9EDC-4362-9909-93CA2C7CF031}" id="{DDF1AFFB-FEAB-425E-9DA7-40A83EF3F3BA}">
+    <text xml:space="preserve">Las cuentas Z_PYGDetallado deben estar a 6 dígitos del PUC y la cuenta 4 debe ser negativa.
+Tenga en cuenta que el nuevo saldo debe ser el valor del mes de los ingresos, los costos y los gastos.
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment7.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A2" dT="2024-05-04T16:41:46.15" personId="{4F71464B-9EDC-4362-9909-93CA2C7CF031}" id="{3BAE724E-6502-4301-B51C-51213B67D22C}">
+    <text xml:space="preserve">Las cuentas Z_PYGDetallado deben estar a 6 dígitos del PUC y la cuenta 4 debe ser negativa.
+El ajuste 1 está relacionado con los ajustes del Ebitda que deban hacerse.  
+Tenga en cuenta que el nuevo saldo debe ser el valor del mes de los ingresos, los costos y los gastos.
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment8.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A2" dT="2024-05-04T16:41:46.15" personId="{4F71464B-9EDC-4362-9909-93CA2C7CF031}" id="{AF05B4E4-3C4F-457D-8348-8261667E1A2D}">
+    <text>Las cuentas Z_PCH son las que se detallan en esta plantilla</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment9.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A2" dT="2024-05-04T16:41:46.15" personId="{4F71464B-9EDC-4362-9909-93CA2C7CF031}" id="{E0AAEAF1-2CE1-4C73-879E-A775F3930A83}">
+    <text>Las cuentas Z_PCH son las que se detallan en esta plantilla</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
@@ -1591,7 +1935,7 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A2" s="8"/>
+      <c r="A2" s="29"/>
       <c r="B2" s="8"/>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -1627,13 +1971,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="27" t="s">
         <v>32</v>
       </c>
       <c r="D1" t="s">
@@ -1641,13 +1985,13 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="28" t="s">
         <v>41</v>
       </c>
       <c r="D2" t="s">
@@ -1655,13 +1999,13 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="28" t="s">
         <v>45</v>
       </c>
       <c r="D3" t="s">
@@ -1669,10 +2013,10 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>48</v>
       </c>
       <c r="D4" t="s">
@@ -1680,7 +2024,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="28" t="s">
         <v>50</v>
       </c>
       <c r="D5" t="s">
@@ -1902,7 +2246,7 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A2" s="8"/>
+      <c r="A2" s="29"/>
       <c r="B2" s="8"/>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -1990,7 +2334,7 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A2" s="8"/>
+      <c r="A2" s="29"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
@@ -2081,7 +2425,7 @@
       </c>
     </row>
     <row r="2" spans="1:11" s="1" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A2" s="15"/>
+      <c r="A2" s="29"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
@@ -2155,9 +2499,9 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="17"/>
+      <c r="A2" s="29"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="16"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
       <c r="F2" s="10"/>
@@ -2186,17 +2530,17 @@
   <dimension ref="A1:K8334"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="11.25"/>
   <cols>
-    <col min="1" max="1" width="13" style="18" customWidth="1"/>
-    <col min="2" max="2" width="15" style="18" customWidth="1"/>
-    <col min="3" max="3" width="13" style="18" customWidth="1"/>
-    <col min="4" max="4" width="16" style="18" customWidth="1"/>
-    <col min="5" max="5" width="13" style="19" customWidth="1"/>
-    <col min="6" max="11" width="13" style="18" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" style="18" customWidth="1"/>
-    <col min="13" max="16384" width="10.5703125" style="18"/>
+    <col min="1" max="1" width="13" style="17" customWidth="1"/>
+    <col min="2" max="2" width="15" style="17" customWidth="1"/>
+    <col min="3" max="3" width="13" style="17" customWidth="1"/>
+    <col min="4" max="4" width="16" style="17" customWidth="1"/>
+    <col min="5" max="5" width="13" style="18" customWidth="1"/>
+    <col min="6" max="11" width="13" style="17" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" style="17" customWidth="1"/>
+    <col min="13" max="16384" width="10.5703125" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="20" customFormat="1" ht="19.5" customHeight="1">
+    <row r="1" spans="1:11" s="19" customFormat="1" ht="19.5" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2232,7 +2576,7 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="12.75" customHeight="1">
-      <c r="A2" s="8"/>
+      <c r="A2" s="29"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
@@ -10607,18 +10951,18 @@
   <dimension ref="A1:K11597"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="11.25"/>
   <cols>
-    <col min="1" max="1" width="13" style="21" customWidth="1"/>
-    <col min="2" max="2" width="15" style="21" customWidth="1"/>
-    <col min="3" max="3" width="13" style="21" customWidth="1"/>
-    <col min="4" max="4" width="16" style="21" customWidth="1"/>
-    <col min="5" max="5" width="13" style="22" customWidth="1"/>
-    <col min="6" max="10" width="13" style="21" customWidth="1"/>
-    <col min="11" max="11" width="13" style="18" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" style="21" customWidth="1"/>
-    <col min="13" max="16384" width="10.5703125" style="21"/>
+    <col min="1" max="1" width="13" style="20" customWidth="1"/>
+    <col min="2" max="2" width="15" style="20" customWidth="1"/>
+    <col min="3" max="3" width="13" style="20" customWidth="1"/>
+    <col min="4" max="4" width="16" style="20" customWidth="1"/>
+    <col min="5" max="5" width="13" style="21" customWidth="1"/>
+    <col min="6" max="10" width="13" style="20" customWidth="1"/>
+    <col min="11" max="11" width="13" style="17" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" style="20" customWidth="1"/>
+    <col min="13" max="16384" width="10.5703125" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="23" customFormat="1" ht="19.5" customHeight="1">
+    <row r="1" spans="1:11" s="22" customFormat="1" ht="19.5" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -10654,7 +10998,7 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="12.75" customHeight="1">
-      <c r="A2" s="8"/>
+      <c r="A2" s="29"/>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
@@ -22293,7 +22637,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="13" style="24" customWidth="1"/>
+    <col min="3" max="3" width="13" style="23" customWidth="1"/>
     <col min="4" max="5" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -22315,17 +22659,17 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A2" s="25">
+      <c r="A2" s="30">
         <v>410</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="25">
         <v>0</v>
       </c>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="8">
@@ -22341,17 +22685,17 @@
       <c r="E3" s="10"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="25">
+      <c r="A4" s="24">
         <v>51100</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="25">
         <v>0</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="8">
@@ -22367,17 +22711,17 @@
       <c r="E5" s="10"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="25">
+      <c r="A6" s="24">
         <v>51200</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="25">
         <v>0</v>
       </c>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="8">
@@ -22393,17 +22737,17 @@
       <c r="E7" s="10"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="25">
+      <c r="A8" s="24">
         <v>51300</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="25">
         <v>0</v>
       </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="8">
@@ -22419,17 +22763,17 @@
       <c r="E9" s="10"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="25">
+      <c r="A10" s="24">
         <v>51400</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="25">
         <v>0</v>
       </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="8">
@@ -22445,17 +22789,17 @@
       <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="25">
+      <c r="A12" s="24">
         <v>51500</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="25">
         <v>0</v>
       </c>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="8">
@@ -22471,17 +22815,17 @@
       <c r="E13" s="10"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="25">
+      <c r="A14" s="24">
         <v>51950</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="25">
         <v>0</v>
       </c>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="8">
@@ -22497,17 +22841,17 @@
       <c r="E15" s="10"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="25">
+      <c r="A16" s="24">
         <v>5199020</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="25">
         <v>0</v>
       </c>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="8">
@@ -22523,17 +22867,17 @@
       <c r="E17" s="10"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="25">
+      <c r="A18" s="24">
         <v>52100</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="25">
         <v>0</v>
       </c>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="8">
@@ -22549,17 +22893,17 @@
       <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="25">
+      <c r="A20" s="24">
         <v>52200</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="25">
         <v>0</v>
       </c>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="8">
@@ -22575,17 +22919,17 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="25">
+      <c r="A22" s="24">
         <v>52300</v>
       </c>
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="25">
         <v>0</v>
       </c>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="8">
@@ -22601,17 +22945,17 @@
       <c r="E23" s="10"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="25">
+      <c r="A24" s="24">
         <v>52400</v>
       </c>
-      <c r="B24" s="25" t="s">
+      <c r="B24" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="25">
         <v>0</v>
       </c>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="8">
@@ -22627,17 +22971,17 @@
       <c r="E25" s="10"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="25">
+      <c r="A26" s="24">
         <v>52500</v>
       </c>
-      <c r="B26" s="25" t="s">
+      <c r="B26" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="25">
         <v>0</v>
       </c>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="8">
@@ -22653,17 +22997,17 @@
       <c r="E27" s="10"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="25">
+      <c r="A28" s="24">
         <v>52950</v>
       </c>
-      <c r="B28" s="25" t="s">
+      <c r="B28" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="25">
         <v>0</v>
       </c>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="8">
@@ -22679,17 +23023,17 @@
       <c r="E29" s="10"/>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="25">
+      <c r="A30" s="24">
         <v>5299020</v>
       </c>
-      <c r="B30" s="25" t="s">
+      <c r="B30" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="26">
+      <c r="C30" s="25">
         <v>0</v>
       </c>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="8">
@@ -22705,17 +23049,17 @@
       <c r="E31" s="10"/>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="25">
+      <c r="A32" s="24">
         <v>42500</v>
       </c>
-      <c r="B32" s="25" t="s">
+      <c r="B32" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C32" s="26">
+      <c r="C32" s="25">
         <v>0</v>
       </c>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="8">
@@ -22731,17 +23075,17 @@
       <c r="E33" s="10"/>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="25">
+      <c r="A34" s="24">
         <v>53100</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B34" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C34" s="26">
+      <c r="C34" s="25">
         <v>0</v>
       </c>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="8">
@@ -22757,17 +23101,17 @@
       <c r="E35" s="10"/>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="25">
+      <c r="A36" s="24">
         <v>53130</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B36" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C36" s="26">
+      <c r="C36" s="25">
         <v>0</v>
       </c>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -22787,8 +23131,9 @@
   <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="13" style="24" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13" style="23" customWidth="1"/>
     <col min="4" max="5" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -22810,17 +23155,17 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A2" s="25">
+      <c r="A2" s="30">
         <v>410</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="26">
+      <c r="C2" s="25">
         <v>0</v>
       </c>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="8">
@@ -22836,17 +23181,17 @@
       <c r="E3" s="10"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="25">
+      <c r="A4" s="24">
         <v>51100</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="25">
         <v>0</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="8">
@@ -22862,17 +23207,17 @@
       <c r="E5" s="10"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="25">
+      <c r="A6" s="24">
         <v>51200</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="25">
         <v>0</v>
       </c>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="8">
@@ -22888,17 +23233,17 @@
       <c r="E7" s="10"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="25">
+      <c r="A8" s="24">
         <v>51300</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="25">
         <v>0</v>
       </c>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="8">
@@ -22914,17 +23259,17 @@
       <c r="E9" s="10"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="25">
+      <c r="A10" s="24">
         <v>51400</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="25">
         <v>0</v>
       </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="8">
@@ -22940,17 +23285,17 @@
       <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="25">
+      <c r="A12" s="24">
         <v>51500</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="25">
         <v>0</v>
       </c>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="8">
@@ -22966,17 +23311,17 @@
       <c r="E13" s="10"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="25">
+      <c r="A14" s="24">
         <v>51950</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="25">
         <v>0</v>
       </c>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="8">
@@ -22992,17 +23337,17 @@
       <c r="E15" s="10"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="25">
+      <c r="A16" s="24">
         <v>5199020</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="25">
         <v>0</v>
       </c>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="8">
@@ -23018,17 +23363,17 @@
       <c r="E17" s="10"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="25">
+      <c r="A18" s="24">
         <v>52100</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="25">
         <v>0</v>
       </c>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="8">
@@ -23044,17 +23389,17 @@
       <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="25">
+      <c r="A20" s="24">
         <v>52200</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="25">
         <v>0</v>
       </c>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="8">
@@ -23070,17 +23415,17 @@
       <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="25">
+      <c r="A22" s="24">
         <v>52300</v>
       </c>
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="25">
         <v>0</v>
       </c>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="8">
@@ -23096,17 +23441,17 @@
       <c r="E23" s="10"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="25">
+      <c r="A24" s="24">
         <v>52400</v>
       </c>
-      <c r="B24" s="25" t="s">
+      <c r="B24" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="25">
         <v>0</v>
       </c>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="8">
@@ -23122,17 +23467,17 @@
       <c r="E25" s="10"/>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="25">
+      <c r="A26" s="24">
         <v>52500</v>
       </c>
-      <c r="B26" s="25" t="s">
+      <c r="B26" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="25">
         <v>0</v>
       </c>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="8">
@@ -23148,17 +23493,17 @@
       <c r="E27" s="10"/>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="25">
+      <c r="A28" s="24">
         <v>52950</v>
       </c>
-      <c r="B28" s="25" t="s">
+      <c r="B28" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="25">
         <v>0</v>
       </c>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="8">
@@ -23174,17 +23519,17 @@
       <c r="E29" s="10"/>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="25">
+      <c r="A30" s="24">
         <v>5299020</v>
       </c>
-      <c r="B30" s="25" t="s">
+      <c r="B30" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="26">
+      <c r="C30" s="25">
         <v>0</v>
       </c>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="8">
@@ -23200,17 +23545,17 @@
       <c r="E31" s="10"/>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="25">
+      <c r="A32" s="24">
         <v>42500</v>
       </c>
-      <c r="B32" s="25" t="s">
+      <c r="B32" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C32" s="26">
+      <c r="C32" s="25">
         <v>0</v>
       </c>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="8">
@@ -23226,17 +23571,17 @@
       <c r="E33" s="10"/>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="25">
+      <c r="A34" s="24">
         <v>53100</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B34" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C34" s="26">
+      <c r="C34" s="25">
         <v>0</v>
       </c>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="8">
@@ -23252,17 +23597,17 @@
       <c r="E35" s="10"/>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="25">
+      <c r="A36" s="24">
         <v>53130</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B36" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C36" s="26">
+      <c r="C36" s="25">
         <v>0</v>
       </c>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
